--- a/docs/deliverables/out/Drop-1_Transactional/BRD-05_Accounting_Disbursement_ACSL/BIBS_TestPlan_BRD-05_Accounting_Disbursement_ACSL_Vol1_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-05_Accounting_Disbursement_ACSL/BIBS_TestPlan_BRD-05_Accounting_Disbursement_ACSL_Vol1_v1.0.xlsx
@@ -16,11 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles and Access" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRS Findings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Document Control'!$A$4:$F$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Document Control'!$4:$4</definedName>
@@ -28,16 +27,14 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Test Conditions'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scenarios'!$A$4:$F$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Scenarios'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$R$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$Q$182</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Test Cases'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$J$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$I$130</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Coverage'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Test Data'!$A$4:$E$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Test Data'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$M$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$L$66</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Roles and Access'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FRS Findings'!$A$4:$D$14</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'FRS Findings'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +435,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -751,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E39"/>
+  <dimension ref="B4:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1010,92 +1007,77 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>10</v>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Legend</t>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>The case ran and the actual result matches the expected result</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>The case ran and the actual result matches the expected result</t>
+          <t>The actual result differs; an issue ID is recorded</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>The actual result differs; a defect ID is recorded</t>
+          <t>The case cannot run (environment, data or an open issue elsewhere)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>The case cannot run (environment, data or a defect elsewhere)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
           <t>Not applicable in this cycle, with the reason in Actual result</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Source: FRS BRD-5 Accounting Disbursement ACSL Vol1. 36 FRs, 90 BRD IDs, 103 test conditions, 9 scenarios, 178 test cases (70 positive, 108 negative).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>Source: FRS BRD-5 (FRS_BRD05_ACCOUNTING_VOL1.md). 36 FRs, 90 BRD IDs, 103 test conditions, 9 scenarios, 178 test cases (70 positive, 108 negative), 103 with an automation reference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Defect ID during execution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="B39" s="20" t="inlineStr">
+          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Issue ID during execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -1111,7 +1093,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId9"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -1124,7 +1105,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -1132,310 +1113,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="25" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>TF-AC-01</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>FR-AC-001</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>The FRS messages "Invalid user ID or password" and "Your account is locked. Contact the System Administrator" (no code) differ from the build ("Invalid user name or password" and "Account is locked. Contact your administrator.", code AUTHENTICATION_FAILED).</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Quote the built messages and the code in FR-AC-001 and Volume 2 FR-DS-001.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>TF-AC-02</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>FR-AC-034</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>The FRS gives "Journal is not balanced - debit &lt;x&gt; vs credit &lt;y&gt;" and "Value date &lt;date&gt; is earlier / later than the permitted &lt;n&gt; back- / forward-dated days"; the build writes "Journal is not balanced: debit ... vs credit ..." and two separate value-date messages ("... is earlier than the permitted &lt;n&gt; back-dated days", "... is later than the permitted &lt;n&gt; forward-dated days"). The number of permitted days is a company setting that the FRS does not name.</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Quote the two value-date messages apart, use the built punctuation and name the company fields (back-dated and forward-dated days) with their delivered values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>TF-AC-03</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>FR-AC-042</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>The FRS message "The broking books of &lt;period&gt; are closed" is not what the user sees; the build names the source module that is locked ("The remittance books of &lt;period&gt; are closed", code BOOKS_CLOSED).</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Change the message to "The &lt;module&gt; books of &lt;period&gt; are closed" in FR-AC-042.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>TF-AC-04</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>FR-AC-050</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>The row message "Row &lt;n&gt; - invalid date / amount '&lt;value&gt;'" is two messages in the build ("Row &lt;n&gt;: invalid date '&lt;value&gt;'" and "Row &lt;n&gt;: invalid amount '&lt;value&gt;'").</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Give the two messages apart with the built punctuation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>TF-AC-05</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>FR-AC-071</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>The FRS messages "Unknown role(s) / permission(s) &lt;list&gt;" and "Permission(s) both added and removed - &lt;list&gt;" differ in punctuation from the build ("Unknown role(s): &lt;list&gt;", "Permission(s) both added and removed: &lt;list&gt;"); FR-AC-072 has the same for ACCESS_APPROVE_INDIVIDUALLY.</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Use the built wording so that testers can compare the text exactly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>TF-AC-06</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>FR-AC-070</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>The FRS and the persona table give the menu path "Administration &gt; Lists of Values" and "Administration &gt; Access Requests"; in BIBS these screens are under Setup &amp; Administration &gt; Broking Setup (with the User Access Matrix).</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Correct the screen paths of FR-AC-070 to FR-AC-072 in FRS v1.1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>TF-AC-07</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>FR-AC-023</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>The FRS lists the paper sizes A4, Letter and Legal and the orientations portrait and landscape. The build also offers A3 and an automatic orientation (by report width), and an unknown value falls back to A4. Acceptance criterion 1 ("shows all its columns on one page width") gives no limit for very wide reports.</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Add A3, the automatic orientation and the fallback to the FRS, and state the smallest font that fit to width may use.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>TF-AC-08</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>FR-AC-011</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>The permission table of section 3.2 gives action classes for the GL permissions (JOURNAL_CREATE and the other journal permissions, COA_UPLOAD, MASTER_MAINTAIN, MASTER_AUTHORIZE, GL_CLOSE_SCHEDULE), but the build leaves the finance permissions unclassified (V890), so the User Access Matrix by action class does not show them.</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Either classify the finance permissions in the build or state in the FRS that the matrix by action class covers the broking areas only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>TF-AC-09</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>FR-AC-054</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>The message of COST_CENTER_MISSING is given only as "&lt;message naming the event and account&gt;"; a tester cannot compare the text.</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Quote the message text the event register shows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>TF-AC-10</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>FR-AC-062</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Acceptance criterion 2 ("The GAP report totals match the open items of the sub-ledger") does not say which open items (receivables and payables of which accounts, at which date, in which currency) are compared.</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Name the sub-ledger accounts and the date basis of the comparison.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:D14"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A5:D514">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Plan BRD-5 Accounting Disbursement ACSL Vol1&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
-    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1584,6 +1264,20 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>Upload-download</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Message</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2079,7 +1773,7 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download</t>
+          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download, Screen, Message</t>
         </is>
       </c>
     </row>
@@ -2096,7 +1790,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
+          <t>Role code and name (and the SIT/UAT user)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2168,7 +1862,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>What the system must do, with the exact message text and, for built BRDs, its code</t>
+          <t>What the system must do, with the exact message text and, where the system shows one, its code</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
@@ -2203,15 +1897,19 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test (class#method) that covers the case; blank when none</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr"/>
+          <t>Execution status</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -2221,19 +1919,15 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>What happened, filled by the tester</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -2243,12 +1937,12 @@
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>What happened, filled by the tester</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr"/>
@@ -2261,12 +1955,12 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Who ran the case</t>
+          <t>Date of the run</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr"/>
@@ -2279,12 +1973,12 @@
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Date of the run</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -2292,17 +1986,17 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Test Cases</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>Defect ID</t>
+          <t>FR / BRD ID</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Defect raised when the case fails</t>
+          <t>FR of the FRS, then BRD requirement ID</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr"/>
@@ -2315,12 +2009,12 @@
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>FR / BRD ID</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>FR of the FRS, then BRD requirement ID</t>
+          <t>FR or BRD ID</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -2333,12 +2027,12 @@
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>FR or BRD ID</t>
+          <t>FR title</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -2351,12 +2045,12 @@
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Traces</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>FR title</t>
+          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -2369,12 +2063,12 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Traces</t>
+          <t>Conditions</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
+          <t>Test conditions</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr"/>
@@ -2387,12 +2081,12 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>Conditions</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Test conditions</t>
+          <t>Cases where the action succeeds</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr"/>
@@ -2405,12 +2099,12 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Cases where the action succeeds</t>
+          <t>Cases where BIBS refuses the action</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr"/>
@@ -2423,12 +2117,12 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Cases where BIBS refuses the action</t>
+          <t>All cases</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr"/>
@@ -2441,30 +2135,34 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>All cases</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr"/>
+          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Covered, GAP</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>Automated</t>
+          <t>Data set</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Cases with an automation reference</t>
+          <t>Data set ID</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
@@ -2472,24 +2170,20 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>Covered, GAP</t>
-        </is>
-      </c>
+          <t>Short name used in the cases</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -2499,12 +2193,12 @@
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>Data set</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Data set ID</t>
+          <t>Records and values in the set</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -2517,12 +2211,12 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Short name used in the cases</t>
+          <t>Seed data set that provides it, or how the tester prepares it; non-production data is masked</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr"/>
@@ -2535,12 +2229,12 @@
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Cases</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Records and values in the set</t>
+          <t>Number of cases that use it</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr"/>
@@ -2548,17 +2242,17 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Case ID</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -2566,17 +2260,17 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>Cases</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Number of cases that use it</t>
+          <t>Screen or action checked</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr"/>
@@ -2589,12 +2283,12 @@
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>Case ID</t>
+          <t>Screen (menu path)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
+          <t>Where it is done</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr"/>
@@ -2607,12 +2301,12 @@
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Permission</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Screen or action checked</t>
+          <t>BIBS permission that grants it</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr"/>
@@ -2625,12 +2319,12 @@
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>Screen (menu path)</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Where it is done</t>
+          <t>Role tested (log in as a user who holds only this role)</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr"/>
@@ -2643,15 +2337,19 @@
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>BIBS permission that grants it</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr"/>
+          <t>Expected access</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Allowed, Denied</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
@@ -2661,12 +2359,12 @@
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Expected result</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Role tested (log in as a user who holds only this role)</t>
+          <t>What the user sees</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr"/>
@@ -2679,17 +2377,17 @@
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Expected access</t>
+          <t>Execution status</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Allowed, Denied</t>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2399,12 @@
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>Expected result</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>What the user sees</t>
+          <t>Filled by the tester</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr"/>
@@ -2719,12 +2417,12 @@
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test, if any</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr"/>
@@ -2737,19 +2435,15 @@
       </c>
       <c r="B64" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>Date of the run</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -2759,144 +2453,18 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Filled by the tester</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr"/>
     </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B66" s="23" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr">
-        <is>
-          <t>Who ran the case</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B67" s="22" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>Date of the run</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B68" s="23" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>Defect raised when the case fails</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>Finding ID</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B70" s="23" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>FR concerned</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B71" s="22" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="inlineStr">
-        <is>
-          <t>Ambiguous or untestable point found while writing the cases</t>
-        </is>
-      </c>
-      <c r="D71" s="12" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B72" s="23" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>What the test team proposes to the FRS owner</t>
-        </is>
-      </c>
-      <c r="D72" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D72"/>
+  <autoFilter ref="A4:D65"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -3006,7 +2574,7 @@
       <c r="E5" s="12" t="inlineStr"/>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Internal draft from FRS BRD-5 Volume 1 v1.0 and the as-built code</t>
+          <t>Internal draft from FRS BRD-5 Volume 1 v1.0</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5411,7 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Every delivered schedule definition runs and exports to Excel and PDF.</t>
+          <t>Every provided schedule definition runs and exports to Excel and PDF.</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
@@ -6833,7 +6401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R182"/>
+  <dimension ref="A1:Q182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6848,12 +6416,11 @@
     <col width="52" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -6888,7 +6455,6 @@
       <c r="O3" s="25" t="n"/>
       <c r="P3" s="25" t="n"/>
       <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -6953,32 +6519,27 @@
       </c>
       <c r="M4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="O4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="P4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -7045,20 +6606,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr">
-        <is>
-          <t>ApiSmokeIT#loginReturnsTokenAndWrongPasswordIsRejected</t>
-        </is>
-      </c>
-      <c r="N5" s="27" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N5" s="12" t="n"/>
       <c r="O5" s="12" t="n"/>
-      <c r="P5" s="12" t="n"/>
-      <c r="Q5" s="28" t="n"/>
-      <c r="R5" s="12" t="n"/>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -7109,7 +6665,7 @@
       <c r="J6" s="12" t="inlineStr">
         <is>
           <t>1. As glofficer, open General Ledger and Planning &amp; Closing in the menu.
-2. Type the address /planning/gl-close.</t>
+2. Open the address of the GL Close &amp; Cut-Off screen directly in the browser.</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
@@ -7122,20 +6678,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="N6" s="27" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N6" s="12" t="n"/>
       <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="28" t="n"/>
-      <c r="R6" s="12" t="n"/>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -7199,20 +6750,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M7" s="12" t="inlineStr">
-        <is>
-          <t>ApiSmokeIT#loginReturnsTokenAndWrongPasswordIsRejected</t>
-        </is>
-      </c>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N7" s="12" t="n"/>
       <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="28" t="n"/>
-      <c r="R7" s="12" t="n"/>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -7276,20 +6822,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr">
-        <is>
-          <t>LoginLockoutTest#theAccountLocksAtTheConfiguredThreshold</t>
-        </is>
-      </c>
-      <c r="N8" s="27" t="inlineStr">
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N8" s="12" t="n"/>
       <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="28" t="n"/>
-      <c r="R8" s="12" t="n"/>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -7350,20 +6891,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr">
-        <is>
-          <t>idleTimer.test.ts#moves from active to warning to expired</t>
-        </is>
-      </c>
-      <c r="N9" s="27" t="inlineStr">
+      <c r="M9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N9" s="12" t="n"/>
       <c r="O9" s="12" t="n"/>
-      <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="28" t="n"/>
-      <c r="R9" s="12" t="n"/>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -7422,20 +6958,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
-        <is>
-          <t>idleTimer.test.ts#warns, then expires and stops ticking</t>
-        </is>
-      </c>
-      <c r="N10" s="27" t="inlineStr">
+      <c r="M10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N10" s="12" t="n"/>
       <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
-      <c r="Q10" s="28" t="n"/>
-      <c r="R10" s="12" t="n"/>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -7499,20 +7030,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr">
-        <is>
-          <t>sessionExpiry.test.ts#warns the configured minutes before the end and expires at the end</t>
-        </is>
-      </c>
-      <c r="N11" s="27" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N11" s="12" t="n"/>
       <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="28" t="n"/>
-      <c r="R11" s="12" t="n"/>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -7571,20 +7097,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M12" s="12" t="inlineStr">
-        <is>
-          <t>SystemAdminIT#everyUserGetsAboutAndSessionPolicyButNotAdministration</t>
-        </is>
-      </c>
-      <c r="N12" s="27" t="inlineStr">
+      <c r="M12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N12" s="12" t="n"/>
       <c r="O12" s="12" t="n"/>
-      <c r="P12" s="12" t="n"/>
-      <c r="Q12" s="28" t="n"/>
-      <c r="R12" s="12" t="n"/>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -7648,20 +7169,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#revaluationRateIsTheMonthEndClosingRateAndBecomesTheNextBookRate</t>
-        </is>
-      </c>
-      <c r="N13" s="27" t="inlineStr">
+      <c r="M13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N13" s="12" t="n"/>
       <c r="O13" s="12" t="n"/>
-      <c r="P13" s="12" t="n"/>
-      <c r="Q13" s="28" t="n"/>
-      <c r="R13" s="12" t="n"/>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -7724,20 +7240,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#revaluationRateIsTheMonthEndClosingRateAndBecomesTheNextBookRate</t>
-        </is>
-      </c>
-      <c r="N14" s="27" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N14" s="12" t="n"/>
       <c r="O14" s="12" t="n"/>
-      <c r="P14" s="12" t="n"/>
-      <c r="Q14" s="28" t="n"/>
-      <c r="R14" s="12" t="n"/>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -7801,16 +7312,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="27" t="inlineStr">
+      <c r="M15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N15" s="12" t="n"/>
       <c r="O15" s="12" t="n"/>
-      <c r="P15" s="12" t="n"/>
-      <c r="Q15" s="28" t="n"/>
-      <c r="R15" s="12" t="n"/>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -7875,16 +7385,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="27" t="inlineStr">
+      <c r="M16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N16" s="12" t="n"/>
       <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="28" t="n"/>
-      <c r="R16" s="12" t="n"/>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -7939,7 +7448,7 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>The revaluation card has no entry action; POST /api/v1/currencies/revaluation-rates returns HTTP 403.</t>
+          <t>The revaluation card has no entry action; a direct request is refused.</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
@@ -7947,20 +7456,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M17" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="N17" s="27" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N17" s="12" t="n"/>
       <c r="O17" s="12" t="n"/>
-      <c r="P17" s="12" t="n"/>
-      <c r="Q17" s="28" t="n"/>
-      <c r="R17" s="12" t="n"/>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -8025,20 +7529,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr">
-        <is>
-          <t>ChartOfAccountsApiIT#accountLifecycleWithMakerCheckerFreezeAndClose</t>
-        </is>
-      </c>
-      <c r="N18" s="27" t="inlineStr">
+      <c r="M18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N18" s="12" t="n"/>
       <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
-      <c r="Q18" s="28" t="n"/>
-      <c r="R18" s="12" t="n"/>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -8101,16 +7600,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="27" t="inlineStr">
+      <c r="M19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N19" s="12" t="n"/>
       <c r="O19" s="12" t="n"/>
-      <c r="P19" s="12" t="n"/>
-      <c r="Q19" s="28" t="n"/>
-      <c r="R19" s="12" t="n"/>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -8174,20 +7672,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M20" s="12" t="inlineStr">
-        <is>
-          <t>ChartOfAccountsApiIT#hierarchyRulesAreEnforced</t>
-        </is>
-      </c>
-      <c r="N20" s="27" t="inlineStr">
+      <c r="M20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N20" s="12" t="n"/>
       <c r="O20" s="12" t="n"/>
-      <c r="P20" s="12" t="n"/>
-      <c r="Q20" s="28" t="n"/>
-      <c r="R20" s="12" t="n"/>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -8251,20 +7744,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr">
-        <is>
-          <t>ChartOfAccountsApiIT#hierarchyRulesAreEnforced</t>
-        </is>
-      </c>
-      <c r="N21" s="27" t="inlineStr">
+      <c r="M21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N21" s="12" t="n"/>
       <c r="O21" s="12" t="n"/>
-      <c r="P21" s="12" t="n"/>
-      <c r="Q21" s="28" t="n"/>
-      <c r="R21" s="12" t="n"/>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -8328,16 +7816,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr"/>
-      <c r="N22" s="27" t="inlineStr">
+      <c r="M22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N22" s="12" t="n"/>
       <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
-      <c r="Q22" s="28" t="n"/>
-      <c r="R22" s="12" t="n"/>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -8401,20 +7888,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M23" s="12" t="inlineStr">
-        <is>
-          <t>ChartOfAccountsApiIT#accountWithPostingsCannotBecomeHeading</t>
-        </is>
-      </c>
-      <c r="N23" s="27" t="inlineStr">
+      <c r="M23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N23" s="12" t="n"/>
       <c r="O23" s="12" t="n"/>
-      <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="28" t="n"/>
-      <c r="R23" s="12" t="n"/>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -8478,20 +7960,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M24" s="12" t="inlineStr">
-        <is>
-          <t>ChartOfAccountsApiIT#makerCannotAuthorizeOwnAccount</t>
-        </is>
-      </c>
-      <c r="N24" s="27" t="inlineStr">
+      <c r="M24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N24" s="12" t="n"/>
       <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="28" t="n"/>
-      <c r="R24" s="12" t="n"/>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -8541,7 +8018,7 @@
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>1. Download the template; upload coa_upload_sample.xlsx; commit.</t>
+          <t>1. Download the template; upload the chart upload example file; commit the valid rows.</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -8554,20 +8031,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M25" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#chartUploadSeedFileLoadsPendingAuthorization</t>
-        </is>
-      </c>
-      <c r="N25" s="27" t="inlineStr">
+      <c r="M25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N25" s="12" t="n"/>
       <c r="O25" s="12" t="n"/>
-      <c r="P25" s="12" t="n"/>
-      <c r="Q25" s="28" t="n"/>
-      <c r="R25" s="12" t="n"/>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -8631,16 +8103,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr"/>
-      <c r="N26" s="27" t="inlineStr">
+      <c r="M26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N26" s="12" t="n"/>
       <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="28" t="n"/>
-      <c r="R26" s="12" t="n"/>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -8704,16 +8175,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M27" s="12" t="inlineStr"/>
-      <c r="N27" s="27" t="inlineStr">
+      <c r="M27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N27" s="12" t="n"/>
       <c r="O27" s="12" t="n"/>
-      <c r="P27" s="12" t="n"/>
-      <c r="Q27" s="28" t="n"/>
-      <c r="R27" s="12" t="n"/>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -8777,16 +8247,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M28" s="12" t="inlineStr"/>
-      <c r="N28" s="27" t="inlineStr">
+      <c r="M28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N28" s="12" t="n"/>
       <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
-      <c r="Q28" s="28" t="n"/>
-      <c r="R28" s="12" t="n"/>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -8850,16 +8319,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M29" s="12" t="inlineStr"/>
-      <c r="N29" s="27" t="inlineStr">
+      <c r="M29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N29" s="12" t="n"/>
       <c r="O29" s="12" t="n"/>
-      <c r="P29" s="12" t="n"/>
-      <c r="Q29" s="28" t="n"/>
-      <c r="R29" s="12" t="n"/>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -8922,16 +8390,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M30" s="12" t="inlineStr"/>
-      <c r="N30" s="27" t="inlineStr">
+      <c r="M30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N30" s="12" t="n"/>
       <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
-      <c r="Q30" s="28" t="n"/>
-      <c r="R30" s="12" t="n"/>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -8995,20 +8462,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr">
-        <is>
-          <t>SpreadsheetRowsTest#rejectsUnsupportedUnreadableAndOversizedFiles</t>
-        </is>
-      </c>
-      <c r="N31" s="27" t="inlineStr">
+      <c r="M31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N31" s="12" t="n"/>
       <c r="O31" s="12" t="n"/>
-      <c r="P31" s="12" t="n"/>
-      <c r="Q31" s="28" t="n"/>
-      <c r="R31" s="12" t="n"/>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -9068,20 +8530,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M32" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#numberingProposesTheNextChildCode; CoaNumberingTest#codesArePaddedAndParsedBack</t>
-        </is>
-      </c>
-      <c r="N32" s="27" t="inlineStr">
+      <c r="M32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N32" s="12" t="n"/>
       <c r="O32" s="12" t="n"/>
-      <c r="P32" s="12" t="n"/>
-      <c r="Q32" s="28" t="n"/>
-      <c r="R32" s="12" t="n"/>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -9140,20 +8597,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr">
-        <is>
-          <t>FinanceReportsIT#mainTrialBalanceBalancesAndRollsUpSubAccounts; AccountHierarchyTest#subAndMicroAccountsRollUpToTheirMainAccount</t>
-        </is>
-      </c>
-      <c r="N33" s="27" t="inlineStr">
+      <c r="M33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N33" s="12" t="n"/>
       <c r="O33" s="12" t="n"/>
-      <c r="P33" s="12" t="n"/>
-      <c r="Q33" s="28" t="n"/>
-      <c r="R33" s="12" t="n"/>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -9213,16 +8665,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M34" s="12" t="inlineStr"/>
-      <c r="N34" s="27" t="inlineStr">
+      <c r="M34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N34" s="12" t="n"/>
       <c r="O34" s="12" t="n"/>
-      <c r="P34" s="12" t="n"/>
-      <c r="Q34" s="28" t="n"/>
-      <c r="R34" s="12" t="n"/>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -9282,16 +8733,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M35" s="12" t="inlineStr"/>
-      <c r="N35" s="27" t="inlineStr">
+      <c r="M35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N35" s="12" t="n"/>
       <c r="O35" s="12" t="n"/>
-      <c r="P35" s="12" t="n"/>
-      <c r="Q35" s="28" t="n"/>
-      <c r="R35" s="12" t="n"/>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -9355,16 +8805,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M36" s="12" t="inlineStr"/>
-      <c r="N36" s="27" t="inlineStr">
+      <c r="M36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N36" s="12" t="n"/>
       <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
-      <c r="Q36" s="28" t="n"/>
-      <c r="R36" s="12" t="n"/>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -9427,20 +8876,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M37" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#chartUploadSeedFileLoadsPendingAuthorization</t>
-        </is>
-      </c>
-      <c r="N37" s="27" t="inlineStr">
+      <c r="M37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N37" s="12" t="n"/>
       <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
-      <c r="Q37" s="28" t="n"/>
-      <c r="R37" s="12" t="n"/>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -9503,20 +8947,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M38" s="12" t="inlineStr">
-        <is>
-          <t>JournalFrbsControlsIT#negativeBalanceControlBlocksOrWarnsAndShortCodesResolve</t>
-        </is>
-      </c>
-      <c r="N38" s="27" t="inlineStr">
+      <c r="M38" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N38" s="12" t="n"/>
       <c r="O38" s="12" t="n"/>
-      <c r="P38" s="12" t="n"/>
-      <c r="Q38" s="28" t="n"/>
-      <c r="R38" s="12" t="n"/>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -9580,16 +9019,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M39" s="12" t="inlineStr"/>
-      <c r="N39" s="27" t="inlineStr">
+      <c r="M39" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N39" s="12" t="n"/>
       <c r="O39" s="12" t="n"/>
-      <c r="P39" s="12" t="n"/>
-      <c r="Q39" s="28" t="n"/>
-      <c r="R39" s="12" t="n"/>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -9653,16 +9091,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M40" s="12" t="inlineStr"/>
-      <c r="N40" s="27" t="inlineStr">
+      <c r="M40" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
-      <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="28" t="n"/>
-      <c r="R40" s="12" t="n"/>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -9722,20 +9159,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M41" s="12" t="inlineStr">
-        <is>
-          <t>FinanceReportsIT#everyFinanceReportRunsAndExportsInAllFormats; ReportArchiveIT#viewOnlyUsersRunButCannotExportAndExportsAreArchivedWithTheirFile</t>
-        </is>
-      </c>
-      <c r="N41" s="27" t="inlineStr">
+      <c r="M41" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="28" t="n"/>
-      <c r="R41" s="12" t="n"/>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -9794,16 +9226,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M42" s="12" t="inlineStr"/>
-      <c r="N42" s="27" t="inlineStr">
+      <c r="M42" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N42" s="12" t="n"/>
       <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
-      <c r="Q42" s="28" t="n"/>
-      <c r="R42" s="12" t="n"/>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -9863,20 +9294,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M43" s="12" t="inlineStr">
-        <is>
-          <t>ReportParametersTest#requiredParameterSentBlankIsRejectedInsteadOfDefaulted</t>
-        </is>
-      </c>
-      <c r="N43" s="27" t="inlineStr">
+      <c r="M43" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N43" s="12" t="n"/>
       <c r="O43" s="12" t="n"/>
-      <c r="P43" s="12" t="n"/>
-      <c r="Q43" s="28" t="n"/>
-      <c r="R43" s="12" t="n"/>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -9927,7 +9353,7 @@
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>The General Ledger reports are not listed; running one through the API returns HTTP 403.</t>
+          <t>The General Ledger reports are not listed; running one by a direct request is refused.</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
@@ -9935,20 +9361,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M44" s="12" t="inlineStr">
-        <is>
-          <t>ReportArchiveIT#usersWithoutTheReportSeeNoRuns</t>
-        </is>
-      </c>
-      <c r="N44" s="27" t="inlineStr">
+      <c r="M44" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N44" s="12" t="n"/>
       <c r="O44" s="12" t="n"/>
-      <c r="P44" s="12" t="n"/>
-      <c r="Q44" s="28" t="n"/>
-      <c r="R44" s="12" t="n"/>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -10008,20 +9429,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M45" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#exportAppliesPrintOptionsAndColumnFilters; reportOptions.test.ts#keeps the matching detail rows only</t>
-        </is>
-      </c>
-      <c r="N45" s="27" t="inlineStr">
+      <c r="M45" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N45" s="12" t="n"/>
       <c r="O45" s="12" t="n"/>
-      <c r="P45" s="12" t="n"/>
-      <c r="Q45" s="28" t="n"/>
-      <c r="R45" s="12" t="n"/>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -10080,20 +9496,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M46" s="12" t="inlineStr">
-        <is>
-          <t>reportOptions.test.ts#keeps every row without a filter</t>
-        </is>
-      </c>
-      <c r="N46" s="27" t="inlineStr">
+      <c r="M46" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N46" s="12" t="n"/>
       <c r="O46" s="12" t="n"/>
-      <c r="P46" s="12" t="n"/>
-      <c r="Q46" s="28" t="n"/>
-      <c r="R46" s="12" t="n"/>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -10152,20 +9563,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#reportBatchZipsTheReportsAndRecordsFailures</t>
-        </is>
-      </c>
-      <c r="N47" s="27" t="inlineStr">
+      <c r="M47" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N47" s="12" t="n"/>
       <c r="O47" s="12" t="n"/>
-      <c r="P47" s="12" t="n"/>
-      <c r="Q47" s="28" t="n"/>
-      <c r="R47" s="12" t="n"/>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -10224,16 +9630,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M48" s="12" t="inlineStr"/>
-      <c r="N48" s="27" t="inlineStr">
+      <c r="M48" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N48" s="12" t="n"/>
       <c r="O48" s="12" t="n"/>
-      <c r="P48" s="12" t="n"/>
-      <c r="Q48" s="28" t="n"/>
-      <c r="R48" s="12" t="n"/>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -10292,20 +9697,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M49" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#reportBatchZipsTheReportsAndRecordsFailures</t>
-        </is>
-      </c>
-      <c r="N49" s="27" t="inlineStr">
+      <c r="M49" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N49" s="12" t="n"/>
       <c r="O49" s="12" t="n"/>
-      <c r="P49" s="12" t="n"/>
-      <c r="Q49" s="28" t="n"/>
-      <c r="R49" s="12" t="n"/>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -10365,16 +9765,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M50" s="12" t="inlineStr"/>
-      <c r="N50" s="27" t="inlineStr">
+      <c r="M50" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N50" s="12" t="n"/>
       <c r="O50" s="12" t="n"/>
-      <c r="P50" s="12" t="n"/>
-      <c r="Q50" s="28" t="n"/>
-      <c r="R50" s="12" t="n"/>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -10414,18 +9813,18 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I51" s="12" t="inlineStr"/>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>1. As gltl, GET /api/v1/reports/batches/{id} of glofficer's batch.</t>
+          <t>1. As gltl, send a direct request to open glofficer's report batch.</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>HTTP 403; the batch does not appear in gltl's list.
+          <t>The request is refused; the batch does not appear in gltl's list.
 Message "You are not permitted to perform this action" (ACCESS_DENIED).</t>
         </is>
       </c>
@@ -10434,16 +9833,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M51" s="12" t="inlineStr"/>
-      <c r="N51" s="27" t="inlineStr">
+      <c r="M51" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N51" s="12" t="n"/>
       <c r="O51" s="12" t="n"/>
-      <c r="P51" s="12" t="n"/>
-      <c r="Q51" s="28" t="n"/>
-      <c r="R51" s="12" t="n"/>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -10502,20 +9900,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M52" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#exportAppliesPrintOptionsAndColumnFilters</t>
-        </is>
-      </c>
-      <c r="N52" s="27" t="inlineStr">
+      <c r="M52" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N52" s="12" t="n"/>
       <c r="O52" s="12" t="n"/>
-      <c r="P52" s="12" t="n"/>
-      <c r="Q52" s="28" t="n"/>
-      <c r="R52" s="12" t="n"/>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -10574,16 +9967,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M53" s="12" t="inlineStr"/>
-      <c r="N53" s="27" t="inlineStr">
+      <c r="M53" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N53" s="12" t="n"/>
       <c r="O53" s="12" t="n"/>
-      <c r="P53" s="12" t="n"/>
-      <c r="Q53" s="28" t="n"/>
-      <c r="R53" s="12" t="n"/>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -10623,7 +10015,7 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I54" s="12" t="inlineStr"/>
@@ -10642,16 +10034,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M54" s="12" t="inlineStr"/>
-      <c r="N54" s="27" t="inlineStr">
+      <c r="M54" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N54" s="12" t="n"/>
       <c r="O54" s="12" t="n"/>
-      <c r="P54" s="12" t="n"/>
-      <c r="Q54" s="28" t="n"/>
-      <c r="R54" s="12" t="n"/>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -10715,20 +10106,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M55" s="12" t="inlineStr">
-        <is>
-          <t>RemittanceIT#anApprovedBatchIsPostedRemittedAndPushedToDisbursement</t>
-        </is>
-      </c>
-      <c r="N55" s="27" t="inlineStr">
+      <c r="M55" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N55" s="12" t="n"/>
       <c r="O55" s="12" t="n"/>
-      <c r="P55" s="12" t="n"/>
-      <c r="Q55" s="28" t="n"/>
-      <c r="R55" s="12" t="n"/>
+      <c r="P55" s="28" t="n"/>
+      <c r="Q55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -10794,16 +10180,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M56" s="12" t="inlineStr"/>
-      <c r="N56" s="27" t="inlineStr">
+      <c r="M56" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N56" s="12" t="n"/>
       <c r="O56" s="12" t="n"/>
-      <c r="P56" s="12" t="n"/>
-      <c r="Q56" s="28" t="n"/>
-      <c r="R56" s="12" t="n"/>
+      <c r="P56" s="28" t="n"/>
+      <c r="Q56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -10867,20 +10252,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M57" s="12" t="inlineStr">
-        <is>
-          <t>AccountingEngineIT#missingAccountRoleFailsAndIsLogged</t>
-        </is>
-      </c>
-      <c r="N57" s="27" t="inlineStr">
+      <c r="M57" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N57" s="12" t="n"/>
       <c r="O57" s="12" t="n"/>
-      <c r="P57" s="12" t="n"/>
-      <c r="Q57" s="28" t="n"/>
-      <c r="R57" s="12" t="n"/>
+      <c r="P57" s="28" t="n"/>
+      <c r="Q57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -10944,16 +10324,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M58" s="12" t="inlineStr"/>
-      <c r="N58" s="27" t="inlineStr">
+      <c r="M58" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N58" s="12" t="n"/>
       <c r="O58" s="12" t="n"/>
-      <c r="P58" s="12" t="n"/>
-      <c r="Q58" s="28" t="n"/>
-      <c r="R58" s="12" t="n"/>
+      <c r="P58" s="28" t="n"/>
+      <c r="Q58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -11016,20 +10395,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M59" s="12" t="inlineStr">
-        <is>
-          <t>JournalLifecycleIT#reversalRestoresBalancesAndMarksOriginal</t>
-        </is>
-      </c>
-      <c r="N59" s="27" t="inlineStr">
+      <c r="M59" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N59" s="12" t="n"/>
       <c r="O59" s="12" t="n"/>
-      <c r="P59" s="12" t="n"/>
-      <c r="Q59" s="28" t="n"/>
-      <c r="R59" s="12" t="n"/>
+      <c r="P59" s="28" t="n"/>
+      <c r="Q59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -11093,20 +10467,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M60" s="12" t="inlineStr">
-        <is>
-          <t>JournalFrbsControlsIT#journalsAreAssignedAndPostedInBulk</t>
-        </is>
-      </c>
-      <c r="N60" s="27" t="inlineStr">
+      <c r="M60" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N60" s="12" t="n"/>
       <c r="O60" s="12" t="n"/>
-      <c r="P60" s="12" t="n"/>
-      <c r="Q60" s="28" t="n"/>
-      <c r="R60" s="12" t="n"/>
+      <c r="P60" s="28" t="n"/>
+      <c r="Q60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -11169,16 +10538,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M61" s="12" t="inlineStr"/>
-      <c r="N61" s="27" t="inlineStr">
+      <c r="M61" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N61" s="12" t="n"/>
       <c r="O61" s="12" t="n"/>
-      <c r="P61" s="12" t="n"/>
-      <c r="Q61" s="28" t="n"/>
-      <c r="R61" s="12" t="n"/>
+      <c r="P61" s="28" t="n"/>
+      <c r="Q61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -11242,20 +10610,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M62" s="12" t="inlineStr">
-        <is>
-          <t>JournalFrbsControlsIT#journalsAreAssignedAndPostedInBulk</t>
-        </is>
-      </c>
-      <c r="N62" s="27" t="inlineStr">
+      <c r="M62" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N62" s="12" t="n"/>
       <c r="O62" s="12" t="n"/>
-      <c r="P62" s="12" t="n"/>
-      <c r="Q62" s="28" t="n"/>
-      <c r="R62" s="12" t="n"/>
+      <c r="P62" s="28" t="n"/>
+      <c r="Q62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -11319,16 +10682,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M63" s="12" t="inlineStr"/>
-      <c r="N63" s="27" t="inlineStr">
+      <c r="M63" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N63" s="12" t="n"/>
       <c r="O63" s="12" t="n"/>
-      <c r="P63" s="12" t="n"/>
-      <c r="Q63" s="28" t="n"/>
-      <c r="R63" s="12" t="n"/>
+      <c r="P63" s="28" t="n"/>
+      <c r="Q63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -11392,20 +10754,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M64" s="12" t="inlineStr">
-        <is>
-          <t>JournalApiIT#rejectCorrectResubmitApproveCopyAndReverse; journalForm.test.ts#leaves out only blank placeholder rows, never lines the user filled in</t>
-        </is>
-      </c>
-      <c r="N64" s="27" t="inlineStr">
+      <c r="M64" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N64" s="12" t="n"/>
       <c r="O64" s="12" t="n"/>
-      <c r="P64" s="12" t="n"/>
-      <c r="Q64" s="28" t="n"/>
-      <c r="R64" s="12" t="n"/>
+      <c r="P64" s="28" t="n"/>
+      <c r="Q64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -11468,20 +10825,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M65" s="12" t="inlineStr">
-        <is>
-          <t>JournalUploadIT#invalidVouchersAreReportedAndSkippedWhileValidOnesAreCreated</t>
-        </is>
-      </c>
-      <c r="N65" s="27" t="inlineStr">
+      <c r="M65" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N65" s="12" t="n"/>
       <c r="O65" s="12" t="n"/>
-      <c r="P65" s="12" t="n"/>
-      <c r="Q65" s="28" t="n"/>
-      <c r="R65" s="12" t="n"/>
+      <c r="P65" s="28" t="n"/>
+      <c r="Q65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -11521,7 +10873,7 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I66" s="12" t="inlineStr">
@@ -11531,7 +10883,7 @@
       </c>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>1. POST /api/v1/journals with journal type SYSTEM.</t>
+          <t>1. Send a direct request to create a journal of type SYSTEM.</t>
         </is>
       </c>
       <c r="K66" s="12" t="inlineStr">
@@ -11545,20 +10897,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M66" s="12" t="inlineStr">
-        <is>
-          <t>JournalApiIT#invalidDimensionAndSystemJournalTypeAreRejected</t>
-        </is>
-      </c>
-      <c r="N66" s="27" t="inlineStr">
+      <c r="M66" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N66" s="12" t="n"/>
       <c r="O66" s="12" t="n"/>
-      <c r="P66" s="12" t="n"/>
-      <c r="Q66" s="28" t="n"/>
-      <c r="R66" s="12" t="n"/>
+      <c r="P66" s="28" t="n"/>
+      <c r="Q66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -11622,16 +10969,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M67" s="12" t="inlineStr"/>
-      <c r="N67" s="27" t="inlineStr">
+      <c r="M67" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N67" s="12" t="n"/>
       <c r="O67" s="12" t="n"/>
-      <c r="P67" s="12" t="n"/>
-      <c r="Q67" s="28" t="n"/>
-      <c r="R67" s="12" t="n"/>
+      <c r="P67" s="28" t="n"/>
+      <c r="Q67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -11695,16 +11041,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M68" s="12" t="inlineStr"/>
-      <c r="N68" s="27" t="inlineStr">
+      <c r="M68" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N68" s="12" t="n"/>
       <c r="O68" s="12" t="n"/>
-      <c r="P68" s="12" t="n"/>
-      <c r="Q68" s="28" t="n"/>
-      <c r="R68" s="12" t="n"/>
+      <c r="P68" s="28" t="n"/>
+      <c r="Q68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -11768,20 +11113,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M69" s="12" t="inlineStr">
-        <is>
-          <t>JournalFrbsControlsIT#accrualIsReversedAutomaticallyOnItsReversalDate</t>
-        </is>
-      </c>
-      <c r="N69" s="27" t="inlineStr">
+      <c r="M69" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N69" s="12" t="n"/>
       <c r="O69" s="12" t="n"/>
-      <c r="P69" s="12" t="n"/>
-      <c r="Q69" s="28" t="n"/>
-      <c r="R69" s="12" t="n"/>
+      <c r="P69" s="28" t="n"/>
+      <c r="Q69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
@@ -11844,20 +11184,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M70" s="12" t="inlineStr">
-        <is>
-          <t>JournalFrbsControlsIT#accrualIsReversedAutomaticallyOnItsReversalDate</t>
-        </is>
-      </c>
-      <c r="N70" s="27" t="inlineStr">
+      <c r="M70" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N70" s="12" t="n"/>
       <c r="O70" s="12" t="n"/>
-      <c r="P70" s="12" t="n"/>
-      <c r="Q70" s="28" t="n"/>
-      <c r="R70" s="12" t="n"/>
+      <c r="P70" s="28" t="n"/>
+      <c r="Q70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -11921,16 +11256,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M71" s="12" t="inlineStr"/>
-      <c r="N71" s="27" t="inlineStr">
+      <c r="M71" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N71" s="12" t="n"/>
       <c r="O71" s="12" t="n"/>
-      <c r="P71" s="12" t="n"/>
-      <c r="Q71" s="28" t="n"/>
-      <c r="R71" s="12" t="n"/>
+      <c r="P71" s="28" t="n"/>
+      <c r="Q71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -11994,20 +11328,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M72" s="12" t="inlineStr">
-        <is>
-          <t>JournalLifecycleIT#unbalancedJournalCannotBeSubmitted; journalMath.test.ts#reports the difference of an unbalanced journal</t>
-        </is>
-      </c>
-      <c r="N72" s="27" t="inlineStr">
+      <c r="M72" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N72" s="12" t="n"/>
       <c r="O72" s="12" t="n"/>
-      <c r="P72" s="12" t="n"/>
-      <c r="Q72" s="28" t="n"/>
-      <c r="R72" s="12" t="n"/>
+      <c r="P72" s="28" t="n"/>
+      <c r="Q72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -12070,20 +11399,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M73" s="12" t="inlineStr">
-        <is>
-          <t>journalMath.test.ts#detects a balanced journal</t>
-        </is>
-      </c>
-      <c r="N73" s="27" t="inlineStr">
+      <c r="M73" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N73" s="12" t="n"/>
       <c r="O73" s="12" t="n"/>
-      <c r="P73" s="12" t="n"/>
-      <c r="Q73" s="28" t="n"/>
-      <c r="R73" s="12" t="n"/>
+      <c r="P73" s="28" t="n"/>
+      <c r="Q73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -12147,20 +11471,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M74" s="12" t="inlineStr">
-        <is>
-          <t>JournalLifecycleIT#accountControlsAreEnforced</t>
-        </is>
-      </c>
-      <c r="N74" s="27" t="inlineStr">
+      <c r="M74" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N74" s="12" t="n"/>
       <c r="O74" s="12" t="n"/>
-      <c r="P74" s="12" t="n"/>
-      <c r="Q74" s="28" t="n"/>
-      <c r="R74" s="12" t="n"/>
+      <c r="P74" s="28" t="n"/>
+      <c r="Q74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -12225,16 +11544,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M75" s="12" t="inlineStr"/>
-      <c r="N75" s="27" t="inlineStr">
+      <c r="M75" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N75" s="12" t="n"/>
       <c r="O75" s="12" t="n"/>
-      <c r="P75" s="12" t="n"/>
-      <c r="Q75" s="28" t="n"/>
-      <c r="R75" s="12" t="n"/>
+      <c r="P75" s="28" t="n"/>
+      <c r="Q75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
@@ -12298,20 +11616,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M76" s="12" t="inlineStr">
-        <is>
-          <t>JournalFrbsControlsIT#negativeBalanceControlBlocksOrWarnsAndShortCodesResolve</t>
-        </is>
-      </c>
-      <c r="N76" s="27" t="inlineStr">
+      <c r="M76" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N76" s="12" t="n"/>
       <c r="O76" s="12" t="n"/>
-      <c r="P76" s="12" t="n"/>
-      <c r="Q76" s="28" t="n"/>
-      <c r="R76" s="12" t="n"/>
+      <c r="P76" s="28" t="n"/>
+      <c r="Q76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -12374,20 +11687,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M77" s="12" t="inlineStr">
-        <is>
-          <t>JournalFrbsControlsIT#negativeBalanceControlBlocksOrWarnsAndShortCodesResolve</t>
-        </is>
-      </c>
-      <c r="N77" s="27" t="inlineStr">
+      <c r="M77" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N77" s="12" t="n"/>
       <c r="O77" s="12" t="n"/>
-      <c r="P77" s="12" t="n"/>
-      <c r="Q77" s="28" t="n"/>
-      <c r="R77" s="12" t="n"/>
+      <c r="P77" s="28" t="n"/>
+      <c r="Q77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
@@ -12446,16 +11754,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M78" s="12" t="inlineStr"/>
-      <c r="N78" s="27" t="inlineStr">
+      <c r="M78" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N78" s="12" t="n"/>
       <c r="O78" s="12" t="n"/>
-      <c r="P78" s="12" t="n"/>
-      <c r="Q78" s="28" t="n"/>
-      <c r="R78" s="12" t="n"/>
+      <c r="P78" s="28" t="n"/>
+      <c r="Q78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
@@ -12514,16 +11821,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M79" s="12" t="inlineStr"/>
-      <c r="N79" s="27" t="inlineStr">
+      <c r="M79" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N79" s="12" t="n"/>
       <c r="O79" s="12" t="n"/>
-      <c r="P79" s="12" t="n"/>
-      <c r="Q79" s="28" t="n"/>
-      <c r="R79" s="12" t="n"/>
+      <c r="P79" s="28" t="n"/>
+      <c r="Q79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
@@ -12582,16 +11888,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M80" s="12" t="inlineStr"/>
-      <c r="N80" s="27" t="inlineStr">
+      <c r="M80" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N80" s="12" t="n"/>
       <c r="O80" s="12" t="n"/>
-      <c r="P80" s="12" t="n"/>
-      <c r="Q80" s="28" t="n"/>
-      <c r="R80" s="12" t="n"/>
+      <c r="P80" s="28" t="n"/>
+      <c r="Q80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -12655,20 +11960,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M81" s="12" t="inlineStr">
-        <is>
-          <t>JournalFrbsControlsIT#journalsAreAssignedAndPostedInBulk</t>
-        </is>
-      </c>
-      <c r="N81" s="27" t="inlineStr">
+      <c r="M81" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N81" s="12" t="n"/>
       <c r="O81" s="12" t="n"/>
-      <c r="P81" s="12" t="n"/>
-      <c r="Q81" s="28" t="n"/>
-      <c r="R81" s="12" t="n"/>
+      <c r="P81" s="28" t="n"/>
+      <c r="Q81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
@@ -12732,20 +12032,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M82" s="12" t="inlineStr">
-        <is>
-          <t>JournalApiIT#rejectCorrectResubmitApproveCopyAndReverse</t>
-        </is>
-      </c>
-      <c r="N82" s="27" t="inlineStr">
+      <c r="M82" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N82" s="12" t="n"/>
       <c r="O82" s="12" t="n"/>
-      <c r="P82" s="12" t="n"/>
-      <c r="Q82" s="28" t="n"/>
-      <c r="R82" s="12" t="n"/>
+      <c r="P82" s="28" t="n"/>
+      <c r="Q82" s="12" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
@@ -12809,16 +12104,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M83" s="12" t="inlineStr"/>
-      <c r="N83" s="27" t="inlineStr">
+      <c r="M83" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N83" s="12" t="n"/>
       <c r="O83" s="12" t="n"/>
-      <c r="P83" s="12" t="n"/>
-      <c r="Q83" s="28" t="n"/>
-      <c r="R83" s="12" t="n"/>
+      <c r="P83" s="28" t="n"/>
+      <c r="Q83" s="12" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
@@ -12882,20 +12176,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M84" s="12" t="inlineStr">
-        <is>
-          <t>JournalLifecycleIT#makerCheckerPostsBalancedJournalToLedger; ApprovalInboxIT#submittedJournalReachesCheckersButNotItsMaker</t>
-        </is>
-      </c>
-      <c r="N84" s="27" t="inlineStr">
+      <c r="M84" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N84" s="12" t="n"/>
       <c r="O84" s="12" t="n"/>
-      <c r="P84" s="12" t="n"/>
-      <c r="Q84" s="28" t="n"/>
-      <c r="R84" s="12" t="n"/>
+      <c r="P84" s="28" t="n"/>
+      <c r="Q84" s="12" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
@@ -12960,20 +12249,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M85" s="12" t="inlineStr">
-        <is>
-          <t>ApprovalInboxIT#journalsAboveTheCheckersLimitAreNotOffered</t>
-        </is>
-      </c>
-      <c r="N85" s="27" t="inlineStr">
+      <c r="M85" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N85" s="12" t="n"/>
       <c r="O85" s="12" t="n"/>
-      <c r="P85" s="12" t="n"/>
-      <c r="Q85" s="28" t="n"/>
-      <c r="R85" s="12" t="n"/>
+      <c r="P85" s="28" t="n"/>
+      <c r="Q85" s="12" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
@@ -13013,7 +12297,7 @@
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I86" s="12" t="inlineStr">
@@ -13023,12 +12307,12 @@
       </c>
       <c r="J86" s="12" t="inlineStr">
         <is>
-          <t>1. POST /api/v1/journals/{id}/approve on a POSTED journal.</t>
+          <t>1. Send a direct request to post a journal that is already POSTED.</t>
         </is>
       </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
-          <t>The call is refused.
+          <t>The request is refused.
 Message "Cannot approve journal JV-2026-00012 in status POSTED" (INVALID_JOURNAL_STATUS).</t>
         </is>
       </c>
@@ -13037,16 +12321,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M86" s="12" t="inlineStr"/>
-      <c r="N86" s="27" t="inlineStr">
+      <c r="M86" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N86" s="12" t="n"/>
       <c r="O86" s="12" t="n"/>
-      <c r="P86" s="12" t="n"/>
-      <c r="Q86" s="28" t="n"/>
-      <c r="R86" s="12" t="n"/>
+      <c r="P86" s="28" t="n"/>
+      <c r="Q86" s="12" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
@@ -13105,20 +12388,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M87" s="12" t="inlineStr">
-        <is>
-          <t>JournalApiIT#rejectCorrectResubmitApproveCopyAndReverse</t>
-        </is>
-      </c>
-      <c r="N87" s="27" t="inlineStr">
+      <c r="M87" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N87" s="12" t="n"/>
       <c r="O87" s="12" t="n"/>
-      <c r="P87" s="12" t="n"/>
-      <c r="Q87" s="28" t="n"/>
-      <c r="R87" s="12" t="n"/>
+      <c r="P87" s="28" t="n"/>
+      <c r="Q87" s="12" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
@@ -13164,12 +12442,12 @@
       <c r="I88" s="12" t="inlineStr"/>
       <c r="J88" s="12" t="inlineStr">
         <is>
-          <t>1. Open a posted journal; PUT /api/v1/journals/{id} with a changed line.</t>
+          <t>1. Open a posted journal; send a direct request to change a line.</t>
         </is>
       </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
-          <t>No Edit action is shown; the call is refused.
+          <t>No Edit action is shown; a direct request is refused.
 Message "Cannot edit journal JV-2026-00012 in status POSTED" (INVALID_JOURNAL_STATUS).</t>
         </is>
       </c>
@@ -13178,16 +12456,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M88" s="12" t="inlineStr"/>
-      <c r="N88" s="27" t="inlineStr">
+      <c r="M88" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N88" s="12" t="n"/>
       <c r="O88" s="12" t="n"/>
-      <c r="P88" s="12" t="n"/>
-      <c r="Q88" s="28" t="n"/>
-      <c r="R88" s="12" t="n"/>
+      <c r="P88" s="28" t="n"/>
+      <c r="Q88" s="12" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
@@ -13246,20 +12523,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M89" s="12" t="inlineStr">
-        <is>
-          <t>JournalLifecycleIT#reversalRestoresBalancesAndMarksOriginal</t>
-        </is>
-      </c>
-      <c r="N89" s="27" t="inlineStr">
+      <c r="M89" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N89" s="12" t="n"/>
       <c r="O89" s="12" t="n"/>
-      <c r="P89" s="12" t="n"/>
-      <c r="Q89" s="28" t="n"/>
-      <c r="R89" s="12" t="n"/>
+      <c r="P89" s="28" t="n"/>
+      <c r="Q89" s="12" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
@@ -13319,20 +12591,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M90" s="12" t="inlineStr">
-        <is>
-          <t>CloseControlsIT#scheduledCloseOfThePreviousMonthRunsThroughTheJob</t>
-        </is>
-      </c>
-      <c r="N90" s="27" t="inlineStr">
+      <c r="M90" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N90" s="12" t="n"/>
       <c r="O90" s="12" t="n"/>
-      <c r="P90" s="12" t="n"/>
-      <c r="Q90" s="28" t="n"/>
-      <c r="R90" s="12" t="n"/>
+      <c r="P90" s="28" t="n"/>
+      <c r="Q90" s="12" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
@@ -13396,20 +12663,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M91" s="12" t="inlineStr">
-        <is>
-          <t>closeTimes.test.ts#accepts only the previous month (FRBS 2.6.1); CloseControlsIT#scheduledCloseOfThePreviousMonthRunsThroughTheJob</t>
-        </is>
-      </c>
-      <c r="N91" s="27" t="inlineStr">
+      <c r="M91" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N91" s="12" t="n"/>
       <c r="O91" s="12" t="n"/>
-      <c r="P91" s="12" t="n"/>
-      <c r="Q91" s="28" t="n"/>
-      <c r="R91" s="12" t="n"/>
+      <c r="P91" s="28" t="n"/>
+      <c r="Q91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
@@ -13469,20 +12731,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M92" s="12" t="inlineStr">
-        <is>
-          <t>CloseControlsIT#refusedCloseIsRecordedAndRaisesTheAlert</t>
-        </is>
-      </c>
-      <c r="N92" s="27" t="inlineStr">
+      <c r="M92" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N92" s="12" t="n"/>
       <c r="O92" s="12" t="n"/>
-      <c r="P92" s="12" t="n"/>
-      <c r="Q92" s="28" t="n"/>
-      <c r="R92" s="12" t="n"/>
+      <c r="P92" s="28" t="n"/>
+      <c r="Q92" s="12" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
@@ -13542,16 +12799,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M93" s="12" t="inlineStr"/>
-      <c r="N93" s="27" t="inlineStr">
+      <c r="M93" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N93" s="12" t="n"/>
       <c r="O93" s="12" t="n"/>
-      <c r="P93" s="12" t="n"/>
-      <c r="Q93" s="28" t="n"/>
-      <c r="R93" s="12" t="n"/>
+      <c r="P93" s="28" t="n"/>
+      <c r="Q93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
@@ -13611,16 +12867,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M94" s="12" t="inlineStr"/>
-      <c r="N94" s="27" t="inlineStr">
+      <c r="M94" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N94" s="12" t="n"/>
       <c r="O94" s="12" t="n"/>
-      <c r="P94" s="12" t="n"/>
-      <c r="Q94" s="28" t="n"/>
-      <c r="R94" s="12" t="n"/>
+      <c r="P94" s="28" t="n"/>
+      <c r="Q94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
@@ -13660,13 +12915,13 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr"/>
       <c r="J95" s="12" t="inlineStr">
         <is>
-          <t>1. POST /api/v1/closing/close-now for a CLOSED period.</t>
+          <t>1. Send a direct request to close a CLOSED period now.</t>
         </is>
       </c>
       <c r="K95" s="12" t="inlineStr">
@@ -13680,16 +12935,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M95" s="12" t="inlineStr"/>
-      <c r="N95" s="27" t="inlineStr">
+      <c r="M95" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N95" s="12" t="n"/>
       <c r="O95" s="12" t="n"/>
-      <c r="P95" s="12" t="n"/>
-      <c r="Q95" s="28" t="n"/>
-      <c r="R95" s="12" t="n"/>
+      <c r="P95" s="28" t="n"/>
+      <c r="Q95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
@@ -13735,12 +12989,12 @@
       <c r="I96" s="12" t="inlineStr"/>
       <c r="J96" s="12" t="inlineStr">
         <is>
-          <t>1. As glofficer, type /planning/gl-close.</t>
+          <t>1. As glofficer, open the address of the GL Close &amp; Cut-Off screen directly in the browser.</t>
         </is>
       </c>
       <c r="K96" s="12" t="inlineStr">
         <is>
-          <t>The screen is refused; POST .../close-schedules returns HTTP 403.</t>
+          <t>The screen is refused; a direct request is refused.</t>
         </is>
       </c>
       <c r="L96" s="12" t="inlineStr">
@@ -13748,20 +13002,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M96" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="N96" s="27" t="inlineStr">
+      <c r="M96" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N96" s="12" t="n"/>
       <c r="O96" s="12" t="n"/>
-      <c r="P96" s="12" t="n"/>
-      <c r="Q96" s="28" t="n"/>
-      <c r="R96" s="12" t="n"/>
+      <c r="P96" s="28" t="n"/>
+      <c r="Q96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
@@ -13820,20 +13069,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M97" s="12" t="inlineStr">
-        <is>
-          <t>YearEndIT#closesProfitAndLossToRetainedEarningsAndOpensNextYear</t>
-        </is>
-      </c>
-      <c r="N97" s="27" t="inlineStr">
+      <c r="M97" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N97" s="12" t="n"/>
       <c r="O97" s="12" t="n"/>
-      <c r="P97" s="12" t="n"/>
-      <c r="Q97" s="28" t="n"/>
-      <c r="R97" s="12" t="n"/>
+      <c r="P97" s="28" t="n"/>
+      <c r="Q97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
@@ -13896,20 +13140,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M98" s="12" t="inlineStr">
-        <is>
-          <t>CloseControlsIT#openPreviousYearRaisesTheYearEndDeadlineAlert</t>
-        </is>
-      </c>
-      <c r="N98" s="27" t="inlineStr">
+      <c r="M98" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N98" s="12" t="n"/>
       <c r="O98" s="12" t="n"/>
-      <c r="P98" s="12" t="n"/>
-      <c r="Q98" s="28" t="n"/>
-      <c r="R98" s="12" t="n"/>
+      <c r="P98" s="28" t="n"/>
+      <c r="Q98" s="12" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
@@ -13969,16 +13208,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M99" s="12" t="inlineStr"/>
-      <c r="N99" s="27" t="inlineStr">
+      <c r="M99" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N99" s="12" t="n"/>
       <c r="O99" s="12" t="n"/>
-      <c r="P99" s="12" t="n"/>
-      <c r="Q99" s="28" t="n"/>
-      <c r="R99" s="12" t="n"/>
+      <c r="P99" s="28" t="n"/>
+      <c r="Q99" s="12" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
@@ -14038,16 +13276,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M100" s="12" t="inlineStr"/>
-      <c r="N100" s="27" t="inlineStr">
+      <c r="M100" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N100" s="12" t="n"/>
       <c r="O100" s="12" t="n"/>
-      <c r="P100" s="12" t="n"/>
-      <c r="Q100" s="28" t="n"/>
-      <c r="R100" s="12" t="n"/>
+      <c r="P100" s="28" t="n"/>
+      <c r="Q100" s="12" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
@@ -14107,16 +13344,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M101" s="12" t="inlineStr"/>
-      <c r="N101" s="27" t="inlineStr">
+      <c r="M101" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N101" s="12" t="n"/>
       <c r="O101" s="12" t="n"/>
-      <c r="P101" s="12" t="n"/>
-      <c r="Q101" s="28" t="n"/>
-      <c r="R101" s="12" t="n"/>
+      <c r="P101" s="28" t="n"/>
+      <c r="Q101" s="12" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
@@ -14177,20 +13413,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M102" s="12" t="inlineStr">
-        <is>
-          <t>CloseControlsIT#closedBrokingBooksRefuseBrokingEventsOnly</t>
-        </is>
-      </c>
-      <c r="N102" s="27" t="inlineStr">
+      <c r="M102" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N102" s="12" t="n"/>
       <c r="O102" s="12" t="n"/>
-      <c r="P102" s="12" t="n"/>
-      <c r="Q102" s="28" t="n"/>
-      <c r="R102" s="12" t="n"/>
+      <c r="P102" s="28" t="n"/>
+      <c r="Q102" s="12" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
@@ -14249,20 +13480,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M103" s="12" t="inlineStr">
-        <is>
-          <t>CloseControlsIT#closedBrokingBooksRefuseBrokingEventsOnly</t>
-        </is>
-      </c>
-      <c r="N103" s="27" t="inlineStr">
+      <c r="M103" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N103" s="12" t="n"/>
       <c r="O103" s="12" t="n"/>
-      <c r="P103" s="12" t="n"/>
-      <c r="Q103" s="28" t="n"/>
-      <c r="R103" s="12" t="n"/>
+      <c r="P103" s="28" t="n"/>
+      <c r="Q103" s="12" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
@@ -14321,16 +13547,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M104" s="12" t="inlineStr"/>
-      <c r="N104" s="27" t="inlineStr">
+      <c r="M104" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N104" s="12" t="n"/>
       <c r="O104" s="12" t="n"/>
-      <c r="P104" s="12" t="n"/>
-      <c r="Q104" s="28" t="n"/>
-      <c r="R104" s="12" t="n"/>
+      <c r="P104" s="28" t="n"/>
+      <c r="Q104" s="12" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
@@ -14390,16 +13615,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M105" s="12" t="inlineStr"/>
-      <c r="N105" s="27" t="inlineStr">
+      <c r="M105" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N105" s="12" t="n"/>
       <c r="O105" s="12" t="n"/>
-      <c r="P105" s="12" t="n"/>
-      <c r="Q105" s="28" t="n"/>
-      <c r="R105" s="12" t="n"/>
+      <c r="P105" s="28" t="n"/>
+      <c r="Q105" s="12" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
@@ -14464,20 +13688,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M106" s="12" t="inlineStr">
-        <is>
-          <t>FxRevaluationIT#revaluesAtClosingRateOncePerPeriodAndAutoReverses; FxRevaluationIT#registerReportRunsAndExports</t>
-        </is>
-      </c>
-      <c r="N106" s="27" t="inlineStr">
+      <c r="M106" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N106" s="12" t="n"/>
       <c r="O106" s="12" t="n"/>
-      <c r="P106" s="12" t="n"/>
-      <c r="Q106" s="28" t="n"/>
-      <c r="R106" s="12" t="n"/>
+      <c r="P106" s="28" t="n"/>
+      <c r="Q106" s="12" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
@@ -14540,20 +13759,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M107" s="12" t="inlineStr">
-        <is>
-          <t>FxRevaluationIT#revaluesAtClosingRateOncePerPeriodAndAutoReverses</t>
-        </is>
-      </c>
-      <c r="N107" s="27" t="inlineStr">
+      <c r="M107" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N107" s="12" t="n"/>
       <c r="O107" s="12" t="n"/>
-      <c r="P107" s="12" t="n"/>
-      <c r="Q107" s="28" t="n"/>
-      <c r="R107" s="12" t="n"/>
+      <c r="P107" s="28" t="n"/>
+      <c r="Q107" s="12" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
@@ -14618,16 +13832,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M108" s="12" t="inlineStr"/>
-      <c r="N108" s="27" t="inlineStr">
+      <c r="M108" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N108" s="12" t="n"/>
       <c r="O108" s="12" t="n"/>
-      <c r="P108" s="12" t="n"/>
-      <c r="Q108" s="28" t="n"/>
-      <c r="R108" s="12" t="n"/>
+      <c r="P108" s="28" t="n"/>
+      <c r="Q108" s="12" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
@@ -14667,7 +13880,7 @@
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
@@ -14677,12 +13890,12 @@
       </c>
       <c r="J109" s="12" t="inlineStr">
         <is>
-          <t>1. POST the revaluation with the period id of another company.</t>
+          <t>1. Send a direct request to save the revaluation with the period of another company.</t>
         </is>
       </c>
       <c r="K109" s="12" t="inlineStr">
         <is>
-          <t>The call is refused.
+          <t>The request is refused.
 Message "Period belongs to another company" (PERIOD_OTHER_COMPANY).</t>
         </is>
       </c>
@@ -14691,16 +13904,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M109" s="12" t="inlineStr"/>
-      <c r="N109" s="27" t="inlineStr">
+      <c r="M109" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N109" s="12" t="n"/>
       <c r="O109" s="12" t="n"/>
-      <c r="P109" s="12" t="n"/>
-      <c r="Q109" s="28" t="n"/>
-      <c r="R109" s="12" t="n"/>
+      <c r="P109" s="28" t="n"/>
+      <c r="Q109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
@@ -14763,20 +13975,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M110" s="12" t="inlineStr">
-        <is>
-          <t>StatementFileImportIT#layoutMapsTheFileAndChequeNumberMatchesOutsideTheDateWindow</t>
-        </is>
-      </c>
-      <c r="N110" s="27" t="inlineStr">
+      <c r="M110" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N110" s="12" t="n"/>
       <c r="O110" s="12" t="n"/>
-      <c r="P110" s="12" t="n"/>
-      <c r="Q110" s="28" t="n"/>
-      <c r="R110" s="12" t="n"/>
+      <c r="P110" s="28" t="n"/>
+      <c r="Q110" s="12" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
@@ -14840,20 +14047,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M111" s="12" t="inlineStr">
-        <is>
-          <t>StatementFileImportIT#layoutMapsTheFileAndChequeNumberMatchesOutsideTheDateWindow; BankReconciliationIT#statementIsMatchedReconciledAndFinalized</t>
-        </is>
-      </c>
-      <c r="N111" s="27" t="inlineStr">
+      <c r="M111" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N111" s="12" t="n"/>
       <c r="O111" s="12" t="n"/>
-      <c r="P111" s="12" t="n"/>
-      <c r="Q111" s="28" t="n"/>
-      <c r="R111" s="12" t="n"/>
+      <c r="P111" s="28" t="n"/>
+      <c r="Q111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
@@ -14917,16 +14119,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M112" s="12" t="inlineStr"/>
-      <c r="N112" s="27" t="inlineStr">
+      <c r="M112" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N112" s="12" t="n"/>
       <c r="O112" s="12" t="n"/>
-      <c r="P112" s="12" t="n"/>
-      <c r="Q112" s="28" t="n"/>
-      <c r="R112" s="12" t="n"/>
+      <c r="P112" s="28" t="n"/>
+      <c r="Q112" s="12" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
@@ -14990,16 +14191,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M113" s="12" t="inlineStr"/>
-      <c r="N113" s="27" t="inlineStr">
+      <c r="M113" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N113" s="12" t="n"/>
       <c r="O113" s="12" t="n"/>
-      <c r="P113" s="12" t="n"/>
-      <c r="Q113" s="28" t="n"/>
-      <c r="R113" s="12" t="n"/>
+      <c r="P113" s="28" t="n"/>
+      <c r="Q113" s="12" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
@@ -15063,20 +14263,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M114" s="12" t="inlineStr">
-        <is>
-          <t>BankReconciliationIT#invalidStatementsAreRejected</t>
-        </is>
-      </c>
-      <c r="N114" s="27" t="inlineStr">
+      <c r="M114" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N114" s="12" t="n"/>
       <c r="O114" s="12" t="n"/>
-      <c r="P114" s="12" t="n"/>
-      <c r="Q114" s="28" t="n"/>
-      <c r="R114" s="12" t="n"/>
+      <c r="P114" s="28" t="n"/>
+      <c r="Q114" s="12" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
@@ -15140,16 +14335,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M115" s="12" t="inlineStr"/>
-      <c r="N115" s="27" t="inlineStr">
+      <c r="M115" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N115" s="12" t="n"/>
       <c r="O115" s="12" t="n"/>
-      <c r="P115" s="12" t="n"/>
-      <c r="Q115" s="28" t="n"/>
-      <c r="R115" s="12" t="n"/>
+      <c r="P115" s="28" t="n"/>
+      <c r="Q115" s="12" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
@@ -15212,20 +14406,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M116" s="12" t="inlineStr">
-        <is>
-          <t>ReceivablesReportsIT#chequeAndBankReportsRunAndExport</t>
-        </is>
-      </c>
-      <c r="N116" s="27" t="inlineStr">
+      <c r="M116" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N116" s="12" t="n"/>
       <c r="O116" s="12" t="n"/>
-      <c r="P116" s="12" t="n"/>
-      <c r="Q116" s="28" t="n"/>
-      <c r="R116" s="12" t="n"/>
+      <c r="P116" s="28" t="n"/>
+      <c r="Q116" s="12" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
@@ -15288,16 +14477,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M117" s="12" t="inlineStr"/>
-      <c r="N117" s="27" t="inlineStr">
+      <c r="M117" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N117" s="12" t="n"/>
       <c r="O117" s="12" t="n"/>
-      <c r="P117" s="12" t="n"/>
-      <c r="Q117" s="28" t="n"/>
-      <c r="R117" s="12" t="n"/>
+      <c r="P117" s="28" t="n"/>
+      <c r="Q117" s="12" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
@@ -15361,20 +14549,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M118" s="12" t="inlineStr">
-        <is>
-          <t>ServiceFeeCalculatorTest#feesAreTheRateOfTheCommissionNetOfWithholdingTax</t>
-        </is>
-      </c>
-      <c r="N118" s="27" t="inlineStr">
+      <c r="M118" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N118" s="12" t="n"/>
       <c r="O118" s="12" t="n"/>
-      <c r="P118" s="12" t="n"/>
-      <c r="Q118" s="28" t="n"/>
-      <c r="R118" s="12" t="n"/>
+      <c r="P118" s="28" t="n"/>
+      <c r="Q118" s="12" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
@@ -15437,20 +14620,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M119" s="12" t="inlineStr">
-        <is>
-          <t>ServiceFeeIT#anApprovedRunIsAccruedPaidReleasedAndLiquidated</t>
-        </is>
-      </c>
-      <c r="N119" s="27" t="inlineStr">
+      <c r="M119" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N119" s="12" t="n"/>
       <c r="O119" s="12" t="n"/>
-      <c r="P119" s="12" t="n"/>
-      <c r="Q119" s="28" t="n"/>
-      <c r="R119" s="12" t="n"/>
+      <c r="P119" s="28" t="n"/>
+      <c r="Q119" s="12" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
@@ -15514,20 +14692,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M120" s="12" t="inlineStr">
-        <is>
-          <t>ServiceFeeIT#theApproverIsNotThePreparerAndAReturnedLineIsSentAgain</t>
-        </is>
-      </c>
-      <c r="N120" s="27" t="inlineStr">
+      <c r="M120" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N120" s="12" t="n"/>
       <c r="O120" s="12" t="n"/>
-      <c r="P120" s="12" t="n"/>
-      <c r="Q120" s="28" t="n"/>
-      <c r="R120" s="12" t="n"/>
+      <c r="P120" s="28" t="n"/>
+      <c r="Q120" s="12" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
@@ -15590,20 +14763,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M121" s="12" t="inlineStr">
-        <is>
-          <t>ServiceFeeIT#aComputedRunIsRecomputedOrCancelledAndFreesItsInvoices</t>
-        </is>
-      </c>
-      <c r="N121" s="27" t="inlineStr">
+      <c r="M121" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N121" s="12" t="n"/>
       <c r="O121" s="12" t="n"/>
-      <c r="P121" s="12" t="n"/>
-      <c r="Q121" s="28" t="n"/>
-      <c r="R121" s="12" t="n"/>
+      <c r="P121" s="28" t="n"/>
+      <c r="Q121" s="12" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
@@ -15667,20 +14835,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M122" s="12" t="inlineStr">
-        <is>
-          <t>ServiceFeeIT#theApproverIsNotThePreparerAndAReturnedLineIsSentAgain</t>
-        </is>
-      </c>
-      <c r="N122" s="27" t="inlineStr">
+      <c r="M122" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N122" s="12" t="n"/>
       <c r="O122" s="12" t="n"/>
-      <c r="P122" s="12" t="n"/>
-      <c r="Q122" s="28" t="n"/>
-      <c r="R122" s="12" t="n"/>
+      <c r="P122" s="28" t="n"/>
+      <c r="Q122" s="12" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="inlineStr">
@@ -15744,20 +14907,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M123" s="12" t="inlineStr">
-        <is>
-          <t>frbs.test.ts#validates the period of a run</t>
-        </is>
-      </c>
-      <c r="N123" s="27" t="inlineStr">
+      <c r="M123" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N123" s="12" t="n"/>
       <c r="O123" s="12" t="n"/>
-      <c r="P123" s="12" t="n"/>
-      <c r="Q123" s="28" t="n"/>
-      <c r="R123" s="12" t="n"/>
+      <c r="P123" s="28" t="n"/>
+      <c r="Q123" s="12" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
@@ -15821,16 +14979,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M124" s="12" t="inlineStr"/>
-      <c r="N124" s="27" t="inlineStr">
+      <c r="M124" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N124" s="12" t="n"/>
       <c r="O124" s="12" t="n"/>
-      <c r="P124" s="12" t="n"/>
-      <c r="Q124" s="28" t="n"/>
-      <c r="R124" s="12" t="n"/>
+      <c r="P124" s="28" t="n"/>
+      <c r="Q124" s="12" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
@@ -15894,20 +15051,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M125" s="12" t="inlineStr">
-        <is>
-          <t>ServiceFeeIT#rulesAndRecipientsAreMaintained; frbs.test.ts#validates a rate</t>
-        </is>
-      </c>
-      <c r="N125" s="27" t="inlineStr">
+      <c r="M125" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N125" s="12" t="n"/>
       <c r="O125" s="12" t="n"/>
-      <c r="P125" s="12" t="n"/>
-      <c r="Q125" s="28" t="n"/>
-      <c r="R125" s="12" t="n"/>
+      <c r="P125" s="28" t="n"/>
+      <c r="Q125" s="12" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="12" t="inlineStr">
@@ -15971,16 +15123,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M126" s="12" t="inlineStr"/>
-      <c r="N126" s="27" t="inlineStr">
+      <c r="M126" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N126" s="12" t="n"/>
       <c r="O126" s="12" t="n"/>
-      <c r="P126" s="12" t="n"/>
-      <c r="Q126" s="28" t="n"/>
-      <c r="R126" s="12" t="n"/>
+      <c r="P126" s="28" t="n"/>
+      <c r="Q126" s="12" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="inlineStr">
@@ -16020,7 +15171,7 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr">
@@ -16030,12 +15181,12 @@
       </c>
       <c r="J127" s="12" t="inlineStr">
         <is>
-          <t>1. POST .../runs/{id}/submit on an APPROVED run.</t>
+          <t>1. Send a direct request to submit an APPROVED run.</t>
         </is>
       </c>
       <c r="K127" s="12" t="inlineStr">
         <is>
-          <t>The call is refused.
+          <t>The request is refused.
 Message "Run no is APPROVED and cannot be submitted" (SERVICE_FEE_STAGE).</t>
         </is>
       </c>
@@ -16044,16 +15195,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M127" s="12" t="inlineStr"/>
-      <c r="N127" s="27" t="inlineStr">
+      <c r="M127" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N127" s="12" t="n"/>
       <c r="O127" s="12" t="n"/>
-      <c r="P127" s="12" t="n"/>
-      <c r="Q127" s="28" t="n"/>
-      <c r="R127" s="12" t="n"/>
+      <c r="P127" s="28" t="n"/>
+      <c r="Q127" s="12" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="inlineStr">
@@ -16117,20 +15267,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M128" s="12" t="inlineStr">
-        <is>
-          <t>ServiceFeeIT#anApprovedRunIsAccruedPaidReleasedAndLiquidated</t>
-        </is>
-      </c>
-      <c r="N128" s="27" t="inlineStr">
+      <c r="M128" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N128" s="12" t="n"/>
       <c r="O128" s="12" t="n"/>
-      <c r="P128" s="12" t="n"/>
-      <c r="Q128" s="28" t="n"/>
-      <c r="R128" s="12" t="n"/>
+      <c r="P128" s="28" t="n"/>
+      <c r="Q128" s="12" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="inlineStr">
@@ -16193,20 +15338,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M129" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#aLiquidationReportIsUploadedOverHttp; ServiceFeeCalculatorTest#aLineIsSentReleasedAndLiquidatedInOrder</t>
-        </is>
-      </c>
-      <c r="N129" s="27" t="inlineStr">
+      <c r="M129" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N129" s="12" t="n"/>
       <c r="O129" s="12" t="n"/>
-      <c r="P129" s="12" t="n"/>
-      <c r="Q129" s="28" t="n"/>
-      <c r="R129" s="12" t="n"/>
+      <c r="P129" s="28" t="n"/>
+      <c r="Q129" s="12" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
@@ -16270,16 +15410,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M130" s="12" t="inlineStr"/>
-      <c r="N130" s="27" t="inlineStr">
+      <c r="M130" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N130" s="12" t="n"/>
       <c r="O130" s="12" t="n"/>
-      <c r="P130" s="12" t="n"/>
-      <c r="Q130" s="28" t="n"/>
-      <c r="R130" s="12" t="n"/>
+      <c r="P130" s="28" t="n"/>
+      <c r="Q130" s="12" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="inlineStr">
@@ -16343,16 +15482,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M131" s="12" t="inlineStr"/>
-      <c r="N131" s="27" t="inlineStr">
+      <c r="M131" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N131" s="12" t="n"/>
       <c r="O131" s="12" t="n"/>
-      <c r="P131" s="12" t="n"/>
-      <c r="Q131" s="28" t="n"/>
-      <c r="R131" s="12" t="n"/>
+      <c r="P131" s="28" t="n"/>
+      <c r="Q131" s="12" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
@@ -16416,16 +15554,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M132" s="12" t="inlineStr"/>
-      <c r="N132" s="27" t="inlineStr">
+      <c r="M132" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N132" s="12" t="n"/>
       <c r="O132" s="12" t="n"/>
-      <c r="P132" s="12" t="n"/>
-      <c r="Q132" s="28" t="n"/>
-      <c r="R132" s="12" t="n"/>
+      <c r="P132" s="28" t="n"/>
+      <c r="Q132" s="12" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="inlineStr">
@@ -16489,20 +15626,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M133" s="12" t="inlineStr">
-        <is>
-          <t>frbs.test.ts#offers the tags a line allows</t>
-        </is>
-      </c>
-      <c r="N133" s="27" t="inlineStr">
+      <c r="M133" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N133" s="12" t="n"/>
       <c r="O133" s="12" t="n"/>
-      <c r="P133" s="12" t="n"/>
-      <c r="Q133" s="28" t="n"/>
-      <c r="R133" s="12" t="n"/>
+      <c r="P133" s="28" t="n"/>
+      <c r="Q133" s="12" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
@@ -16565,20 +15697,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M134" s="12" t="inlineStr">
-        <is>
-          <t>CostCenterRuleIT#missingCostCentreFailsTheEventUntilARuleProvidesIt</t>
-        </is>
-      </c>
-      <c r="N134" s="27" t="inlineStr">
+      <c r="M134" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N134" s="12" t="n"/>
       <c r="O134" s="12" t="n"/>
-      <c r="P134" s="12" t="n"/>
-      <c r="Q134" s="28" t="n"/>
-      <c r="R134" s="12" t="n"/>
+      <c r="P134" s="28" t="n"/>
+      <c r="Q134" s="12" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="12" t="inlineStr">
@@ -16644,20 +15771,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M135" s="12" t="inlineStr">
-        <is>
-          <t>CostCenterRuleIT#missingCostCentreFailsTheEventUntilARuleProvidesIt</t>
-        </is>
-      </c>
-      <c r="N135" s="27" t="inlineStr">
+      <c r="M135" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N135" s="12" t="n"/>
       <c r="O135" s="12" t="n"/>
-      <c r="P135" s="12" t="n"/>
-      <c r="Q135" s="28" t="n"/>
-      <c r="R135" s="12" t="n"/>
+      <c r="P135" s="28" t="n"/>
+      <c r="Q135" s="12" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="inlineStr">
@@ -16721,20 +15843,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M136" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#costCentreRulesAndEmployeesAreMaintained</t>
-        </is>
-      </c>
-      <c r="N136" s="27" t="inlineStr">
+      <c r="M136" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N136" s="12" t="n"/>
       <c r="O136" s="12" t="n"/>
-      <c r="P136" s="12" t="n"/>
-      <c r="Q136" s="28" t="n"/>
-      <c r="R136" s="12" t="n"/>
+      <c r="P136" s="28" t="n"/>
+      <c r="Q136" s="12" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
@@ -16794,20 +15911,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M137" s="12" t="inlineStr">
-        <is>
-          <t>RemittanceOperationsIT#aWithIncentivesBatchDeductsTheEarlyRemittanceIncentive</t>
-        </is>
-      </c>
-      <c r="N137" s="27" t="inlineStr">
+      <c r="M137" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N137" s="12" t="n"/>
       <c r="O137" s="12" t="n"/>
-      <c r="P137" s="12" t="n"/>
-      <c r="Q137" s="28" t="n"/>
-      <c r="R137" s="12" t="n"/>
+      <c r="P137" s="28" t="n"/>
+      <c r="Q137" s="12" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="12" t="inlineStr">
@@ -16866,16 +15978,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M138" s="12" t="inlineStr"/>
-      <c r="N138" s="27" t="inlineStr">
+      <c r="M138" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N138" s="12" t="n"/>
       <c r="O138" s="12" t="n"/>
-      <c r="P138" s="12" t="n"/>
-      <c r="Q138" s="28" t="n"/>
-      <c r="R138" s="12" t="n"/>
+      <c r="P138" s="28" t="n"/>
+      <c r="Q138" s="12" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
@@ -16934,16 +16045,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M139" s="12" t="inlineStr"/>
-      <c r="N139" s="27" t="inlineStr">
+      <c r="M139" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N139" s="12" t="n"/>
       <c r="O139" s="12" t="n"/>
-      <c r="P139" s="12" t="n"/>
-      <c r="Q139" s="28" t="n"/>
-      <c r="R139" s="12" t="n"/>
+      <c r="P139" s="28" t="n"/>
+      <c r="Q139" s="12" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="12" t="inlineStr">
@@ -17002,20 +16112,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M140" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#everyReportOfThePackExportsToExcelAndPdf; frbs.test.ts#groups the pack, links and exports its entries</t>
-        </is>
-      </c>
-      <c r="N140" s="27" t="inlineStr">
+      <c r="M140" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N140" s="12" t="n"/>
       <c r="O140" s="12" t="n"/>
-      <c r="P140" s="12" t="n"/>
-      <c r="Q140" s="28" t="n"/>
-      <c r="R140" s="12" t="n"/>
+      <c r="P140" s="28" t="n"/>
+      <c r="Q140" s="12" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="12" t="inlineStr">
@@ -17074,20 +16179,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M141" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#everyReportOfThePackExportsToExcelAndPdf</t>
-        </is>
-      </c>
-      <c r="N141" s="27" t="inlineStr">
+      <c r="M141" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N141" s="12" t="n"/>
       <c r="O141" s="12" t="n"/>
-      <c r="P141" s="12" t="n"/>
-      <c r="Q141" s="28" t="n"/>
-      <c r="R141" s="12" t="n"/>
+      <c r="P141" s="28" t="n"/>
+      <c r="Q141" s="12" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="12" t="inlineStr">
@@ -17133,7 +16233,7 @@
       <c r="I142" s="12" t="inlineStr"/>
       <c r="J142" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as disb; type /frbs.</t>
+          <t>1. Log in as disb; open the address of the FRBS Report Pack directly in the browser.</t>
         </is>
       </c>
       <c r="K142" s="12" t="inlineStr">
@@ -17146,20 +16246,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M142" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="N142" s="27" t="inlineStr">
+      <c r="M142" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N142" s="12" t="n"/>
       <c r="O142" s="12" t="n"/>
-      <c r="P142" s="12" t="n"/>
-      <c r="Q142" s="28" t="n"/>
-      <c r="R142" s="12" t="n"/>
+      <c r="P142" s="28" t="n"/>
+      <c r="Q142" s="12" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="12" t="inlineStr">
@@ -17184,7 +16279,7 @@
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>Every delivered definition runs</t>
+          <t>Every provided definition runs</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
@@ -17218,20 +16313,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M143" s="12" t="inlineStr">
-        <is>
-          <t>AccountScheduleIT#everySeededScheduleRunsAndExportsToExcelAndPdf</t>
-        </is>
-      </c>
-      <c r="N143" s="27" t="inlineStr">
+      <c r="M143" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N143" s="12" t="n"/>
       <c r="O143" s="12" t="n"/>
-      <c r="P143" s="12" t="n"/>
-      <c r="Q143" s="28" t="n"/>
-      <c r="R143" s="12" t="n"/>
+      <c r="P143" s="28" t="n"/>
+      <c r="Q143" s="12" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="12" t="inlineStr">
@@ -17290,20 +16380,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M144" s="12" t="inlineStr">
-        <is>
-          <t>AccountScheduleIT#premiumReceivablesAreAgedPerPartyAndTheBucketsAddUpToTheBalance</t>
-        </is>
-      </c>
-      <c r="N144" s="27" t="inlineStr">
+      <c r="M144" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N144" s="12" t="n"/>
       <c r="O144" s="12" t="n"/>
-      <c r="P144" s="12" t="n"/>
-      <c r="Q144" s="28" t="n"/>
-      <c r="R144" s="12" t="n"/>
+      <c r="P144" s="28" t="n"/>
+      <c r="Q144" s="12" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="12" t="inlineStr">
@@ -17363,20 +16448,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M145" s="12" t="inlineStr">
-        <is>
-          <t>AccountScheduleIT#definitionsAndCommentaryAreMaintained</t>
-        </is>
-      </c>
-      <c r="N145" s="27" t="inlineStr">
+      <c r="M145" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N145" s="12" t="n"/>
       <c r="O145" s="12" t="n"/>
-      <c r="P145" s="12" t="n"/>
-      <c r="Q145" s="28" t="n"/>
-      <c r="R145" s="12" t="n"/>
+      <c r="P145" s="28" t="n"/>
+      <c r="Q145" s="12" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="12" t="inlineStr">
@@ -17436,20 +16516,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M146" s="12" t="inlineStr">
-        <is>
-          <t>ScheduleMathTest#definitionsAreValidatedAndNormalised; frbs.test.ts#validates a schedule definition</t>
-        </is>
-      </c>
-      <c r="N146" s="27" t="inlineStr">
+      <c r="M146" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N146" s="12" t="n"/>
       <c r="O146" s="12" t="n"/>
-      <c r="P146" s="12" t="n"/>
-      <c r="Q146" s="28" t="n"/>
-      <c r="R146" s="12" t="n"/>
+      <c r="P146" s="28" t="n"/>
+      <c r="Q146" s="12" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="12" t="inlineStr">
@@ -17509,16 +16584,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M147" s="12" t="inlineStr"/>
-      <c r="N147" s="27" t="inlineStr">
+      <c r="M147" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N147" s="12" t="n"/>
       <c r="O147" s="12" t="n"/>
-      <c r="P147" s="12" t="n"/>
-      <c r="Q147" s="28" t="n"/>
-      <c r="R147" s="12" t="n"/>
+      <c r="P147" s="28" t="n"/>
+      <c r="Q147" s="12" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="12" t="inlineStr">
@@ -17578,16 +16652,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M148" s="12" t="inlineStr"/>
-      <c r="N148" s="27" t="inlineStr">
+      <c r="M148" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N148" s="12" t="n"/>
       <c r="O148" s="12" t="n"/>
-      <c r="P148" s="12" t="n"/>
-      <c r="Q148" s="28" t="n"/>
-      <c r="R148" s="12" t="n"/>
+      <c r="P148" s="28" t="n"/>
+      <c r="Q148" s="12" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="12" t="inlineStr">
@@ -17647,16 +16720,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M149" s="12" t="inlineStr"/>
-      <c r="N149" s="27" t="inlineStr">
+      <c r="M149" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N149" s="12" t="n"/>
       <c r="O149" s="12" t="n"/>
-      <c r="P149" s="12" t="n"/>
-      <c r="Q149" s="28" t="n"/>
-      <c r="R149" s="12" t="n"/>
+      <c r="P149" s="28" t="n"/>
+      <c r="Q149" s="12" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="12" t="inlineStr">
@@ -17716,20 +16788,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M150" s="12" t="inlineStr">
-        <is>
-          <t>ScheduleMathTest#commentsNeedACommentaryScheduleAMonthAndARow</t>
-        </is>
-      </c>
-      <c r="N150" s="27" t="inlineStr">
+      <c r="M150" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N150" s="12" t="n"/>
       <c r="O150" s="12" t="n"/>
-      <c r="P150" s="12" t="n"/>
-      <c r="Q150" s="28" t="n"/>
-      <c r="R150" s="12" t="n"/>
+      <c r="P150" s="28" t="n"/>
+      <c r="Q150" s="12" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="12" t="inlineStr">
@@ -17788,20 +16855,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M151" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#everyReportOfThePackExportsToExcelAndPdf</t>
-        </is>
-      </c>
-      <c r="N151" s="27" t="inlineStr">
+      <c r="M151" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N151" s="12" t="n"/>
       <c r="O151" s="12" t="n"/>
-      <c r="P151" s="12" t="n"/>
-      <c r="Q151" s="28" t="n"/>
-      <c r="R151" s="12" t="n"/>
+      <c r="P151" s="28" t="n"/>
+      <c r="Q151" s="12" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="12" t="inlineStr">
@@ -17860,16 +16922,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M152" s="12" t="inlineStr"/>
-      <c r="N152" s="27" t="inlineStr">
+      <c r="M152" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N152" s="12" t="n"/>
       <c r="O152" s="12" t="n"/>
-      <c r="P152" s="12" t="n"/>
-      <c r="Q152" s="28" t="n"/>
-      <c r="R152" s="12" t="n"/>
+      <c r="P152" s="28" t="n"/>
+      <c r="Q152" s="12" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="12" t="inlineStr">
@@ -17928,16 +16989,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M153" s="12" t="inlineStr"/>
-      <c r="N153" s="27" t="inlineStr">
+      <c r="M153" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N153" s="12" t="n"/>
       <c r="O153" s="12" t="n"/>
-      <c r="P153" s="12" t="n"/>
-      <c r="Q153" s="28" t="n"/>
-      <c r="R153" s="12" t="n"/>
+      <c r="P153" s="28" t="n"/>
+      <c r="Q153" s="12" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="12" t="inlineStr">
@@ -17996,20 +17056,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M154" s="12" t="inlineStr">
-        <is>
-          <t>ReportParametersTest#reversedDateAndNumberRangesAreRejected</t>
-        </is>
-      </c>
-      <c r="N154" s="27" t="inlineStr">
+      <c r="M154" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N154" s="12" t="n"/>
       <c r="O154" s="12" t="n"/>
-      <c r="P154" s="12" t="n"/>
-      <c r="Q154" s="28" t="n"/>
-      <c r="R154" s="12" t="n"/>
+      <c r="P154" s="28" t="n"/>
+      <c r="Q154" s="12" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="12" t="inlineStr">
@@ -18068,20 +17123,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M155" s="12" t="inlineStr">
-        <is>
-          <t>BirOutputsIT#everyNewBirOutputIsGeneratedAndExportedToExcelAndPdf</t>
-        </is>
-      </c>
-      <c r="N155" s="27" t="inlineStr">
+      <c r="M155" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N155" s="12" t="n"/>
       <c r="O155" s="12" t="n"/>
-      <c r="P155" s="12" t="n"/>
-      <c r="Q155" s="28" t="n"/>
-      <c r="R155" s="12" t="n"/>
+      <c r="P155" s="28" t="n"/>
+      <c r="Q155" s="12" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="12" t="inlineStr">
@@ -18140,20 +17190,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M156" s="12" t="inlineStr">
-        <is>
-          <t>BirOutputsIT#aCertificateIsPostedListedInTheSawtAndCancelled</t>
-        </is>
-      </c>
-      <c r="N156" s="27" t="inlineStr">
+      <c r="M156" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N156" s="12" t="n"/>
       <c r="O156" s="12" t="n"/>
-      <c r="P156" s="12" t="n"/>
-      <c r="Q156" s="28" t="n"/>
-      <c r="R156" s="12" t="n"/>
+      <c r="P156" s="28" t="n"/>
+      <c r="Q156" s="12" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="12" t="inlineStr">
@@ -18212,16 +17257,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M157" s="12" t="inlineStr"/>
-      <c r="N157" s="27" t="inlineStr">
+      <c r="M157" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N157" s="12" t="n"/>
       <c r="O157" s="12" t="n"/>
-      <c r="P157" s="12" t="n"/>
-      <c r="Q157" s="28" t="n"/>
-      <c r="R157" s="12" t="n"/>
+      <c r="P157" s="28" t="n"/>
+      <c r="Q157" s="12" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="12" t="inlineStr">
@@ -18281,20 +17325,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M158" s="12" t="inlineStr">
-        <is>
-          <t>TaxMathTest#invalidPeriodsAreRejected</t>
-        </is>
-      </c>
-      <c r="N158" s="27" t="inlineStr">
+      <c r="M158" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N158" s="12" t="n"/>
       <c r="O158" s="12" t="n"/>
-      <c r="P158" s="12" t="n"/>
-      <c r="Q158" s="28" t="n"/>
-      <c r="R158" s="12" t="n"/>
+      <c r="P158" s="28" t="n"/>
+      <c r="Q158" s="12" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="12" t="inlineStr">
@@ -18354,16 +17393,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M159" s="12" t="inlineStr"/>
-      <c r="N159" s="27" t="inlineStr">
+      <c r="M159" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N159" s="12" t="n"/>
       <c r="O159" s="12" t="n"/>
-      <c r="P159" s="12" t="n"/>
-      <c r="Q159" s="28" t="n"/>
-      <c r="R159" s="12" t="n"/>
+      <c r="P159" s="28" t="n"/>
+      <c r="Q159" s="12" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="12" t="inlineStr">
@@ -18423,16 +17461,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M160" s="12" t="inlineStr"/>
-      <c r="N160" s="27" t="inlineStr">
+      <c r="M160" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N160" s="12" t="n"/>
       <c r="O160" s="12" t="n"/>
-      <c r="P160" s="12" t="n"/>
-      <c r="Q160" s="28" t="n"/>
-      <c r="R160" s="12" t="n"/>
+      <c r="P160" s="28" t="n"/>
+      <c r="Q160" s="12" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="12" t="inlineStr">
@@ -18483,7 +17520,7 @@
       </c>
       <c r="K161" s="12" t="inlineStr">
         <is>
-          <t>BIR Forms &amp; Books is not offered; the report call returns HTTP 403.</t>
+          <t>BIR Forms &amp; Books is not offered; a direct report request is refused.</t>
         </is>
       </c>
       <c r="L161" s="12" t="inlineStr">
@@ -18491,20 +17528,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M161" s="12" t="inlineStr">
-        <is>
-          <t>TaxApiIT#usersWithoutTaxPermissionsAreRefused</t>
-        </is>
-      </c>
-      <c r="N161" s="27" t="inlineStr">
+      <c r="M161" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N161" s="12" t="n"/>
       <c r="O161" s="12" t="n"/>
-      <c r="P161" s="12" t="n"/>
-      <c r="Q161" s="28" t="n"/>
-      <c r="R161" s="12" t="n"/>
+      <c r="P161" s="28" t="n"/>
+      <c r="Q161" s="12" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="12" t="inlineStr">
@@ -18568,20 +17600,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M162" s="12" t="inlineStr">
-        <is>
-          <t>LovServiceIT#newValueIsUsableOnlyAfterAuthorizationAndWithinEffectivity</t>
-        </is>
-      </c>
-      <c r="N162" s="27" t="inlineStr">
+      <c r="M162" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N162" s="12" t="n"/>
       <c r="O162" s="12" t="n"/>
-      <c r="P162" s="12" t="n"/>
-      <c r="Q162" s="28" t="n"/>
-      <c r="R162" s="12" t="n"/>
+      <c r="P162" s="28" t="n"/>
+      <c r="Q162" s="12" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="12" t="inlineStr">
@@ -18644,20 +17671,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M163" s="12" t="inlineStr">
-        <is>
-          <t>LovServiceIT#newValueIsUsableOnlyAfterAuthorizationAndWithinEffectivity</t>
-        </is>
-      </c>
-      <c r="N163" s="27" t="inlineStr">
+      <c r="M163" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N163" s="12" t="n"/>
       <c r="O163" s="12" t="n"/>
-      <c r="P163" s="12" t="n"/>
-      <c r="Q163" s="28" t="n"/>
-      <c r="R163" s="12" t="n"/>
+      <c r="P163" s="28" t="n"/>
+      <c r="Q163" s="12" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="12" t="inlineStr">
@@ -18721,20 +17743,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M164" s="12" t="inlineStr">
-        <is>
-          <t>LovServiceIT#rejectsDuplicatesInvalidDatesAndOptionalBlank</t>
-        </is>
-      </c>
-      <c r="N164" s="27" t="inlineStr">
+      <c r="M164" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N164" s="12" t="n"/>
       <c r="O164" s="12" t="n"/>
-      <c r="P164" s="12" t="n"/>
-      <c r="Q164" s="28" t="n"/>
-      <c r="R164" s="12" t="n"/>
+      <c r="P164" s="28" t="n"/>
+      <c r="Q164" s="12" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="12" t="inlineStr">
@@ -18774,7 +17791,7 @@
       </c>
       <c r="H165" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I165" s="12" t="inlineStr">
@@ -18784,12 +17801,12 @@
       </c>
       <c r="J165" s="12" t="inlineStr">
         <is>
-          <t>1. POST a value to a list maintained by the system.</t>
+          <t>1. Send a direct request to add a value to a list maintained by the system.</t>
         </is>
       </c>
       <c r="K165" s="12" t="inlineStr">
         <is>
-          <t>The call is refused.
+          <t>The request is refused.
 Message "The list type is maintained by the system" (LOV_NOT_MAINTAINABLE).</t>
         </is>
       </c>
@@ -18798,16 +17815,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M165" s="12" t="inlineStr"/>
-      <c r="N165" s="27" t="inlineStr">
+      <c r="M165" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N165" s="12" t="n"/>
       <c r="O165" s="12" t="n"/>
-      <c r="P165" s="12" t="n"/>
-      <c r="Q165" s="28" t="n"/>
-      <c r="R165" s="12" t="n"/>
+      <c r="P165" s="28" t="n"/>
+      <c r="Q165" s="12" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="12" t="inlineStr">
@@ -18872,20 +17888,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M166" s="12" t="inlineStr">
-        <is>
-          <t>ApprovalInboxIT#pendingMasterDataIsOfferedToAuthorizersOtherThanTheMaker</t>
-        </is>
-      </c>
-      <c r="N166" s="27" t="inlineStr">
+      <c r="M166" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N166" s="12" t="n"/>
       <c r="O166" s="12" t="n"/>
-      <c r="P166" s="12" t="n"/>
-      <c r="Q166" s="28" t="n"/>
-      <c r="R166" s="12" t="n"/>
+      <c r="P166" s="28" t="n"/>
+      <c r="Q166" s="12" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="12" t="inlineStr">
@@ -18950,20 +17961,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M167" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestIT#createdUserIsAppliedOnApprovalWithATemporaryPassword; AccessRequestIT#accessMatrixListsRolesAgainstPermissions</t>
-        </is>
-      </c>
-      <c r="N167" s="27" t="inlineStr">
+      <c r="M167" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N167" s="12" t="n"/>
       <c r="O167" s="12" t="n"/>
-      <c r="P167" s="12" t="n"/>
-      <c r="Q167" s="28" t="n"/>
-      <c r="R167" s="12" t="n"/>
+      <c r="P167" s="28" t="n"/>
+      <c r="Q167" s="12" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="12" t="inlineStr">
@@ -19027,20 +18033,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M168" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestIT#requestsAreValidatedAndDecidedUnderFourEyes; accessRequest.test.ts#needs the new user data, a group profile, the remarks and the approver to submit</t>
-        </is>
-      </c>
-      <c r="N168" s="27" t="inlineStr">
+      <c r="M168" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N168" s="12" t="n"/>
       <c r="O168" s="12" t="n"/>
-      <c r="P168" s="12" t="n"/>
-      <c r="Q168" s="28" t="n"/>
-      <c r="R168" s="12" t="n"/>
+      <c r="P168" s="28" t="n"/>
+      <c r="Q168" s="12" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="12" t="inlineStr">
@@ -19104,16 +18105,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M169" s="12" t="inlineStr"/>
-      <c r="N169" s="27" t="inlineStr">
+      <c r="M169" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N169" s="12" t="n"/>
       <c r="O169" s="12" t="n"/>
-      <c r="P169" s="12" t="n"/>
-      <c r="Q169" s="28" t="n"/>
-      <c r="R169" s="12" t="n"/>
+      <c r="P169" s="28" t="n"/>
+      <c r="Q169" s="12" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="12" t="inlineStr">
@@ -19177,16 +18177,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M170" s="12" t="inlineStr"/>
-      <c r="N170" s="27" t="inlineStr">
+      <c r="M170" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N170" s="12" t="n"/>
       <c r="O170" s="12" t="n"/>
-      <c r="P170" s="12" t="n"/>
-      <c r="Q170" s="28" t="n"/>
-      <c r="R170" s="12" t="n"/>
+      <c r="P170" s="28" t="n"/>
+      <c r="Q170" s="12" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="12" t="inlineStr">
@@ -19226,7 +18225,7 @@
       </c>
       <c r="H171" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I171" s="12" t="inlineStr">
@@ -19250,16 +18249,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M171" s="12" t="inlineStr"/>
-      <c r="N171" s="27" t="inlineStr">
+      <c r="M171" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N171" s="12" t="n"/>
       <c r="O171" s="12" t="n"/>
-      <c r="P171" s="12" t="n"/>
-      <c r="Q171" s="28" t="n"/>
-      <c r="R171" s="12" t="n"/>
+      <c r="P171" s="28" t="n"/>
+      <c r="Q171" s="12" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="12" t="inlineStr">
@@ -19323,16 +18321,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M172" s="12" t="inlineStr"/>
-      <c r="N172" s="27" t="inlineStr">
+      <c r="M172" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N172" s="12" t="n"/>
       <c r="O172" s="12" t="n"/>
-      <c r="P172" s="12" t="n"/>
-      <c r="Q172" s="28" t="n"/>
-      <c r="R172" s="12" t="n"/>
+      <c r="P172" s="28" t="n"/>
+      <c r="Q172" s="12" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="12" t="inlineStr">
@@ -19388,7 +18385,7 @@
       <c r="K173" s="12" t="inlineStr">
         <is>
           <t>The request is refused.
-Message "The request does not change the permissions of role FRBS_TL" (ACCESS_NO_PERMISSION_CHANGE).</t>
+Message "The request does not change the permissions of group profile FRBS Team Lead" (ACCESS_NO_PERMISSION_CHANGE).</t>
         </is>
       </c>
       <c r="L173" s="12" t="inlineStr">
@@ -19396,16 +18393,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M173" s="12" t="inlineStr"/>
-      <c r="N173" s="27" t="inlineStr">
+      <c r="M173" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N173" s="12" t="n"/>
       <c r="O173" s="12" t="n"/>
-      <c r="P173" s="12" t="n"/>
-      <c r="Q173" s="28" t="n"/>
-      <c r="R173" s="12" t="n"/>
+      <c r="P173" s="28" t="n"/>
+      <c r="Q173" s="12" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="12" t="inlineStr">
@@ -19469,20 +18465,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M174" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestIT#requestsAreValidatedAndDecidedUnderFourEyes</t>
-        </is>
-      </c>
-      <c r="N174" s="27" t="inlineStr">
+      <c r="M174" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N174" s="12" t="n"/>
       <c r="O174" s="12" t="n"/>
-      <c r="P174" s="12" t="n"/>
-      <c r="Q174" s="28" t="n"/>
-      <c r="R174" s="12" t="n"/>
+      <c r="P174" s="28" t="n"/>
+      <c r="Q174" s="12" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="12" t="inlineStr">
@@ -19545,20 +18536,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M175" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestReturnIT#returnedRequestIsResubmittedAndApprovedInBulk</t>
-        </is>
-      </c>
-      <c r="N175" s="27" t="inlineStr">
+      <c r="M175" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N175" s="12" t="n"/>
       <c r="O175" s="12" t="n"/>
-      <c r="P175" s="12" t="n"/>
-      <c r="Q175" s="28" t="n"/>
-      <c r="R175" s="12" t="n"/>
+      <c r="P175" s="28" t="n"/>
+      <c r="Q175" s="12" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
@@ -19622,16 +18608,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M176" s="12" t="inlineStr"/>
-      <c r="N176" s="27" t="inlineStr">
+      <c r="M176" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N176" s="12" t="n"/>
       <c r="O176" s="12" t="n"/>
-      <c r="P176" s="12" t="n"/>
-      <c r="Q176" s="28" t="n"/>
-      <c r="R176" s="12" t="n"/>
+      <c r="P176" s="28" t="n"/>
+      <c r="Q176" s="12" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="12" t="inlineStr">
@@ -19695,20 +18680,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M177" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestReturnIT#returnedRequestIsResubmittedAndApprovedInBulk</t>
-        </is>
-      </c>
-      <c r="N177" s="27" t="inlineStr">
+      <c r="M177" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N177" s="12" t="n"/>
       <c r="O177" s="12" t="n"/>
-      <c r="P177" s="12" t="n"/>
-      <c r="Q177" s="28" t="n"/>
-      <c r="R177" s="12" t="n"/>
+      <c r="P177" s="28" t="n"/>
+      <c r="Q177" s="12" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="12" t="inlineStr">
@@ -19772,16 +18752,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M178" s="12" t="inlineStr"/>
-      <c r="N178" s="27" t="inlineStr">
+      <c r="M178" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N178" s="12" t="n"/>
       <c r="O178" s="12" t="n"/>
-      <c r="P178" s="12" t="n"/>
-      <c r="Q178" s="28" t="n"/>
-      <c r="R178" s="12" t="n"/>
+      <c r="P178" s="28" t="n"/>
+      <c r="Q178" s="12" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="12" t="inlineStr">
@@ -19845,16 +18824,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M179" s="12" t="inlineStr"/>
-      <c r="N179" s="27" t="inlineStr">
+      <c r="M179" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N179" s="12" t="n"/>
       <c r="O179" s="12" t="n"/>
-      <c r="P179" s="12" t="n"/>
-      <c r="Q179" s="28" t="n"/>
-      <c r="R179" s="12" t="n"/>
+      <c r="P179" s="28" t="n"/>
+      <c r="Q179" s="12" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="12" t="inlineStr">
@@ -19919,20 +18897,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M180" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestIT#requestsAreValidatedAndDecidedUnderFourEyes</t>
-        </is>
-      </c>
-      <c r="N180" s="27" t="inlineStr">
+      <c r="M180" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N180" s="12" t="n"/>
       <c r="O180" s="12" t="n"/>
-      <c r="P180" s="12" t="n"/>
-      <c r="Q180" s="28" t="n"/>
-      <c r="R180" s="12" t="n"/>
+      <c r="P180" s="28" t="n"/>
+      <c r="Q180" s="12" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="12" t="inlineStr">
@@ -19972,7 +18945,7 @@
       </c>
       <c r="H181" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I181" s="12" t="inlineStr">
@@ -19982,12 +18955,12 @@
       </c>
       <c r="J181" s="12" t="inlineStr">
         <is>
-          <t>1. POST .../access-requests/{id}/approve on an APPROVED request.</t>
+          <t>1. Send a direct request to approve an APPROVED access request.</t>
         </is>
       </c>
       <c r="K181" s="12" t="inlineStr">
         <is>
-          <t>The call is refused.
+          <t>The request is refused.
 Message "Request no is already APPROVED" (ACCESS_REQUEST_DECIDED).</t>
         </is>
       </c>
@@ -19996,16 +18969,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M181" s="12" t="inlineStr"/>
-      <c r="N181" s="27" t="inlineStr">
+      <c r="M181" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N181" s="12" t="n"/>
       <c r="O181" s="12" t="n"/>
-      <c r="P181" s="12" t="n"/>
-      <c r="Q181" s="28" t="n"/>
-      <c r="R181" s="12" t="n"/>
+      <c r="P181" s="28" t="n"/>
+      <c r="Q181" s="12" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="12" t="inlineStr">
@@ -20069,23 +19041,22 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M182" s="12" t="inlineStr"/>
-      <c r="N182" s="27" t="inlineStr">
+      <c r="M182" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N182" s="12" t="n"/>
       <c r="O182" s="12" t="n"/>
-      <c r="P182" s="12" t="n"/>
-      <c r="Q182" s="28" t="n"/>
-      <c r="R182" s="12" t="n"/>
+      <c r="P182" s="28" t="n"/>
+      <c r="Q182" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R182"/>
+  <autoFilter ref="A4:Q182"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A2:Q2"/>
   </mergeCells>
-  <conditionalFormatting sqref="N5:N682">
+  <conditionalFormatting sqref="M5:M682">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -20099,19 +19070,19 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:R682">
+  <conditionalFormatting sqref="A5:Q682">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="F5:F682" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
-      <formula1>'_lists'!$B$1:$B$7</formula1>
+      <formula1>'_lists'!$B$1:$B$9</formula1>
     </dataValidation>
     <dataValidation sqref="L5:L682" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'_lists'!$C$1:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N682" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="M5:M682" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$D$1:$D$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -20135,7 +19106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20147,7 +19118,6 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -20174,7 +19144,6 @@
       <c r="G3" s="25" t="n"/>
       <c r="H3" s="25" t="n"/>
       <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -20219,11 +19188,6 @@
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="J4" s="26" t="inlineStr">
-        <is>
           <t>Coverage</t>
         </is>
       </c>
@@ -20261,10 +19225,7 @@
       <c r="H5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I5" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20303,10 +19264,7 @@
       <c r="H6" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" s="27" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20345,10 +19303,7 @@
       <c r="H7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20387,10 +19342,7 @@
       <c r="H8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I8" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" s="27" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20429,10 +19381,7 @@
       <c r="H9" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I9" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="27" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20471,10 +19420,7 @@
       <c r="H10" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I10" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="27" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20513,10 +19459,7 @@
       <c r="H11" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" s="27" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20555,10 +19498,7 @@
       <c r="H12" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="27" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20597,10 +19537,7 @@
       <c r="H13" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="27" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20639,10 +19576,7 @@
       <c r="H14" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="27" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20681,10 +19615,7 @@
       <c r="H15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="27" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20723,10 +19654,7 @@
       <c r="H16" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" s="27" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20765,10 +19693,7 @@
       <c r="H17" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20807,10 +19732,7 @@
       <c r="H18" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I18" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="27" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20849,10 +19771,7 @@
       <c r="H19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="27" t="inlineStr">
+      <c r="I19" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20891,10 +19810,7 @@
       <c r="H20" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" s="27" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20933,10 +19849,7 @@
       <c r="H21" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="27" t="inlineStr">
+      <c r="I21" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20975,10 +19888,7 @@
       <c r="H22" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I22" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="27" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21017,10 +19927,7 @@
       <c r="H23" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="27" t="inlineStr">
+      <c r="I23" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21059,10 +19966,7 @@
       <c r="H24" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="27" t="inlineStr">
+      <c r="I24" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21101,10 +20005,7 @@
       <c r="H25" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="27" t="inlineStr">
+      <c r="I25" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21143,10 +20044,7 @@
       <c r="H26" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="27" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21185,10 +20083,7 @@
       <c r="H27" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" s="27" t="inlineStr">
+      <c r="I27" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21227,10 +20122,7 @@
       <c r="H28" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="27" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21269,10 +20161,7 @@
       <c r="H29" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="27" t="inlineStr">
+      <c r="I29" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21311,10 +20200,7 @@
       <c r="H30" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J30" s="27" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21353,10 +20239,7 @@
       <c r="H31" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" s="27" t="inlineStr">
+      <c r="I31" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21395,10 +20278,7 @@
       <c r="H32" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I32" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="27" t="inlineStr">
+      <c r="I32" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21437,10 +20317,7 @@
       <c r="H33" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="27" t="inlineStr">
+      <c r="I33" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21479,10 +20356,7 @@
       <c r="H34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J34" s="27" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21521,10 +20395,7 @@
       <c r="H35" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J35" s="27" t="inlineStr">
+      <c r="I35" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21563,10 +20434,7 @@
       <c r="H36" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="27" t="inlineStr">
+      <c r="I36" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21605,10 +20473,7 @@
       <c r="H37" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J37" s="27" t="inlineStr">
+      <c r="I37" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21647,10 +20512,7 @@
       <c r="H38" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J38" s="27" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21689,10 +20551,7 @@
       <c r="H39" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I39" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J39" s="27" t="inlineStr">
+      <c r="I39" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21731,10 +20590,7 @@
       <c r="H40" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" s="27" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21769,10 +20625,7 @@
       <c r="H41" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" s="27" t="inlineStr">
+      <c r="I41" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21807,10 +20660,7 @@
       <c r="H42" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I42" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J42" s="27" t="inlineStr">
+      <c r="I42" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21845,10 +20695,7 @@
       <c r="H43" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I43" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" s="27" t="inlineStr">
+      <c r="I43" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21883,10 +20730,7 @@
       <c r="H44" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J44" s="27" t="inlineStr">
+      <c r="I44" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21921,10 +20765,7 @@
       <c r="H45" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I45" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J45" s="27" t="inlineStr">
+      <c r="I45" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21959,10 +20800,7 @@
       <c r="H46" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I46" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J46" s="27" t="inlineStr">
+      <c r="I46" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21997,10 +20835,7 @@
       <c r="H47" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I47" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J47" s="27" t="inlineStr">
+      <c r="I47" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22035,10 +20870,7 @@
       <c r="H48" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I48" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J48" s="27" t="inlineStr">
+      <c r="I48" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22073,10 +20905,7 @@
       <c r="H49" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I49" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J49" s="27" t="inlineStr">
+      <c r="I49" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22111,10 +20940,7 @@
       <c r="H50" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I50" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J50" s="27" t="inlineStr">
+      <c r="I50" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22149,10 +20975,7 @@
       <c r="H51" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I51" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J51" s="27" t="inlineStr">
+      <c r="I51" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22187,10 +21010,7 @@
       <c r="H52" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I52" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J52" s="27" t="inlineStr">
+      <c r="I52" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22225,10 +21045,7 @@
       <c r="H53" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I53" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J53" s="27" t="inlineStr">
+      <c r="I53" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22263,10 +21080,7 @@
       <c r="H54" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J54" s="27" t="inlineStr">
+      <c r="I54" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22301,10 +21115,7 @@
       <c r="H55" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J55" s="27" t="inlineStr">
+      <c r="I55" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22339,10 +21150,7 @@
       <c r="H56" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I56" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J56" s="27" t="inlineStr">
+      <c r="I56" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22377,10 +21185,7 @@
       <c r="H57" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I57" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J57" s="27" t="inlineStr">
+      <c r="I57" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22415,10 +21220,7 @@
       <c r="H58" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I58" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" s="27" t="inlineStr">
+      <c r="I58" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22453,10 +21255,7 @@
       <c r="H59" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I59" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J59" s="27" t="inlineStr">
+      <c r="I59" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22491,10 +21290,7 @@
       <c r="H60" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I60" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" s="27" t="inlineStr">
+      <c r="I60" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22529,10 +21325,7 @@
       <c r="H61" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I61" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" s="27" t="inlineStr">
+      <c r="I61" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22567,10 +21360,7 @@
       <c r="H62" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I62" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J62" s="27" t="inlineStr">
+      <c r="I62" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22605,10 +21395,7 @@
       <c r="H63" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I63" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J63" s="27" t="inlineStr">
+      <c r="I63" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22643,10 +21430,7 @@
       <c r="H64" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I64" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J64" s="27" t="inlineStr">
+      <c r="I64" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22681,10 +21465,7 @@
       <c r="H65" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I65" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J65" s="27" t="inlineStr">
+      <c r="I65" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22719,10 +21500,7 @@
       <c r="H66" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I66" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J66" s="27" t="inlineStr">
+      <c r="I66" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22757,10 +21535,7 @@
       <c r="H67" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J67" s="27" t="inlineStr">
+      <c r="I67" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22795,10 +21570,7 @@
       <c r="H68" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I68" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J68" s="27" t="inlineStr">
+      <c r="I68" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22833,10 +21605,7 @@
       <c r="H69" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I69" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J69" s="27" t="inlineStr">
+      <c r="I69" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22871,10 +21640,7 @@
       <c r="H70" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I70" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J70" s="27" t="inlineStr">
+      <c r="I70" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22909,10 +21675,7 @@
       <c r="H71" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I71" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J71" s="27" t="inlineStr">
+      <c r="I71" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22947,10 +21710,7 @@
       <c r="H72" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I72" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J72" s="27" t="inlineStr">
+      <c r="I72" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22985,10 +21745,7 @@
       <c r="H73" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I73" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J73" s="27" t="inlineStr">
+      <c r="I73" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23023,10 +21780,7 @@
       <c r="H74" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I74" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J74" s="27" t="inlineStr">
+      <c r="I74" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23061,10 +21815,7 @@
       <c r="H75" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I75" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J75" s="27" t="inlineStr">
+      <c r="I75" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23099,10 +21850,7 @@
       <c r="H76" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I76" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" s="27" t="inlineStr">
+      <c r="I76" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23137,10 +21885,7 @@
       <c r="H77" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I77" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J77" s="27" t="inlineStr">
+      <c r="I77" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23175,10 +21920,7 @@
       <c r="H78" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I78" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J78" s="27" t="inlineStr">
+      <c r="I78" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23213,10 +21955,7 @@
       <c r="H79" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I79" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J79" s="27" t="inlineStr">
+      <c r="I79" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23251,10 +21990,7 @@
       <c r="H80" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I80" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="27" t="inlineStr">
+      <c r="I80" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23289,10 +22025,7 @@
       <c r="H81" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I81" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J81" s="27" t="inlineStr">
+      <c r="I81" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23327,10 +22060,7 @@
       <c r="H82" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I82" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="27" t="inlineStr">
+      <c r="I82" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23365,10 +22095,7 @@
       <c r="H83" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I83" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J83" s="27" t="inlineStr">
+      <c r="I83" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23403,10 +22130,7 @@
       <c r="H84" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I84" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J84" s="27" t="inlineStr">
+      <c r="I84" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23441,10 +22165,7 @@
       <c r="H85" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I85" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J85" s="27" t="inlineStr">
+      <c r="I85" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23479,10 +22200,7 @@
       <c r="H86" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I86" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J86" s="27" t="inlineStr">
+      <c r="I86" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23517,10 +22235,7 @@
       <c r="H87" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I87" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J87" s="27" t="inlineStr">
+      <c r="I87" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23555,10 +22270,7 @@
       <c r="H88" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I88" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J88" s="27" t="inlineStr">
+      <c r="I88" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23593,10 +22305,7 @@
       <c r="H89" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I89" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J89" s="27" t="inlineStr">
+      <c r="I89" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23631,10 +22340,7 @@
       <c r="H90" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I90" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J90" s="27" t="inlineStr">
+      <c r="I90" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23669,10 +22375,7 @@
       <c r="H91" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I91" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J91" s="27" t="inlineStr">
+      <c r="I91" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23707,10 +22410,7 @@
       <c r="H92" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I92" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J92" s="27" t="inlineStr">
+      <c r="I92" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23745,10 +22445,7 @@
       <c r="H93" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I93" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J93" s="27" t="inlineStr">
+      <c r="I93" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23783,10 +22480,7 @@
       <c r="H94" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I94" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J94" s="27" t="inlineStr">
+      <c r="I94" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23821,10 +22515,7 @@
       <c r="H95" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I95" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="27" t="inlineStr">
+      <c r="I95" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23859,10 +22550,7 @@
       <c r="H96" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I96" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J96" s="27" t="inlineStr">
+      <c r="I96" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23897,10 +22585,7 @@
       <c r="H97" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I97" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J97" s="27" t="inlineStr">
+      <c r="I97" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23935,10 +22620,7 @@
       <c r="H98" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="27" t="inlineStr">
+      <c r="I98" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23973,10 +22655,7 @@
       <c r="H99" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I99" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J99" s="27" t="inlineStr">
+      <c r="I99" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24011,10 +22690,7 @@
       <c r="H100" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I100" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J100" s="27" t="inlineStr">
+      <c r="I100" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24049,10 +22725,7 @@
       <c r="H101" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I101" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J101" s="27" t="inlineStr">
+      <c r="I101" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24087,10 +22760,7 @@
       <c r="H102" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I102" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J102" s="27" t="inlineStr">
+      <c r="I102" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24125,10 +22795,7 @@
       <c r="H103" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I103" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J103" s="27" t="inlineStr">
+      <c r="I103" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24163,10 +22830,7 @@
       <c r="H104" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I104" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J104" s="27" t="inlineStr">
+      <c r="I104" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24201,10 +22865,7 @@
       <c r="H105" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I105" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J105" s="27" t="inlineStr">
+      <c r="I105" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24239,10 +22900,7 @@
       <c r="H106" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I106" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J106" s="27" t="inlineStr">
+      <c r="I106" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24277,10 +22935,7 @@
       <c r="H107" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I107" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J107" s="27" t="inlineStr">
+      <c r="I107" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24315,10 +22970,7 @@
       <c r="H108" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I108" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J108" s="27" t="inlineStr">
+      <c r="I108" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24353,10 +23005,7 @@
       <c r="H109" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I109" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J109" s="27" t="inlineStr">
+      <c r="I109" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24391,10 +23040,7 @@
       <c r="H110" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I110" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J110" s="27" t="inlineStr">
+      <c r="I110" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24429,10 +23075,7 @@
       <c r="H111" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I111" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J111" s="27" t="inlineStr">
+      <c r="I111" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24467,10 +23110,7 @@
       <c r="H112" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I112" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J112" s="27" t="inlineStr">
+      <c r="I112" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24505,10 +23145,7 @@
       <c r="H113" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I113" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J113" s="27" t="inlineStr">
+      <c r="I113" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24543,10 +23180,7 @@
       <c r="H114" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="27" t="inlineStr">
+      <c r="I114" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24581,10 +23215,7 @@
       <c r="H115" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I115" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J115" s="27" t="inlineStr">
+      <c r="I115" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24619,10 +23250,7 @@
       <c r="H116" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I116" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J116" s="27" t="inlineStr">
+      <c r="I116" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24657,10 +23285,7 @@
       <c r="H117" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I117" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J117" s="27" t="inlineStr">
+      <c r="I117" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24695,10 +23320,7 @@
       <c r="H118" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I118" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J118" s="27" t="inlineStr">
+      <c r="I118" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24733,10 +23355,7 @@
       <c r="H119" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I119" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J119" s="27" t="inlineStr">
+      <c r="I119" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24771,10 +23390,7 @@
       <c r="H120" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I120" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" s="27" t="inlineStr">
+      <c r="I120" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24809,10 +23425,7 @@
       <c r="H121" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I121" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J121" s="27" t="inlineStr">
+      <c r="I121" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24847,10 +23460,7 @@
       <c r="H122" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I122" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J122" s="27" t="inlineStr">
+      <c r="I122" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24885,10 +23495,7 @@
       <c r="H123" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I123" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J123" s="27" t="inlineStr">
+      <c r="I123" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24923,10 +23530,7 @@
       <c r="H124" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I124" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J124" s="27" t="inlineStr">
+      <c r="I124" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24961,10 +23565,7 @@
       <c r="H125" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I125" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J125" s="27" t="inlineStr">
+      <c r="I125" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24999,10 +23600,7 @@
       <c r="H126" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I126" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J126" s="27" t="inlineStr">
+      <c r="I126" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25037,10 +23635,7 @@
       <c r="H127" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I127" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J127" s="27" t="inlineStr">
+      <c r="I127" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25075,10 +23670,7 @@
       <c r="H128" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I128" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J128" s="27" t="inlineStr">
+      <c r="I128" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25113,10 +23705,7 @@
       <c r="H129" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I129" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J129" s="27" t="inlineStr">
+      <c r="I129" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -25151,32 +23740,29 @@
       <c r="H130" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I130" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J130" s="27" t="inlineStr">
+      <c r="I130" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J130"/>
+  <autoFilter ref="A4:I130"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J630">
+  <conditionalFormatting sqref="I5:I630">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"GAP"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:J630">
+  <conditionalFormatting sqref="A5:I630">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J630" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
+    <dataValidation sqref="I5:I630" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
       <formula1>'_lists'!$E$1:$E$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -25276,7 +23862,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Seeds V999 (BRD-5 users), V980, V990, V900; grants V890 and V899</t>
+          <t>Seed data (BRD-5, broking, Operations, administrator and auditor users, with their grants)</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -25301,7 +23887,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Seeds V900, V901 and V999</t>
+          <t>Seed data (chart of accounts and posting rules)</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
@@ -25321,12 +23907,12 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Base currency PHP; USD active with BOOK and CLOSING rates; parameter OPS_BOOK_RATE_SOURCE as delivered</t>
+          <t>Base currency PHP; USD active with BOOK and CLOSING rates; parameter OPS_BOOK_RATE_SOURCE at its default</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Seed V900 and the currency master</t>
+          <t>Seed data and the currency master</t>
         </is>
       </c>
       <c r="E7" s="12" t="n">
@@ -25346,12 +23932,12 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>coa_upload_sample.xlsx with 8 parent and child accounts, among them 1913.01 with short code PRUSDBP (WARN negative-balance policy); a copy with one row whose parent is missing</t>
+          <t>The chart upload example file with 8 parent and child accounts, among them 1913.01 with short code PRUSDBP (WARN negative-balance policy); a copy with one row whose parent is missing</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>docs/samples/coa_upload_sample.xlsx (the copy is prepared by the test lead)</t>
+          <t>Example file of the Chart Upload screen (the copy is prepared by the test lead)</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
@@ -25401,7 +23987,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Migration V898 and seed runner FrbsSeedData</t>
+          <t>Service fee rules and a seed run as configured for the SIT environment</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -25426,7 +24012,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Receivables seed (ReceivablesSeedData) and a file prepared by the test lead</t>
+          <t>Seed data (receivables) and a file prepared by the test lead</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
@@ -25451,7 +24037,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Migrations of the lists (V750, V890 onwards); requests keyed in by the tester</t>
+          <t>Lists of values as configured for the SIT environment; requests keyed in by the tester</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
@@ -25488,7 +24074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -25498,12 +24084,11 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -25533,7 +24118,6 @@
       <c r="J3" s="25" t="n"/>
       <c r="K3" s="25" t="n"/>
       <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -25573,32 +24157,27 @@
       </c>
       <c r="H4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="J4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="K4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="L4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="M4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -25638,20 +24217,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="12" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -25689,20 +24263,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="H6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="28" t="n"/>
-      <c r="M6" s="12" t="n"/>
+      <c r="K6" s="28" t="n"/>
+      <c r="L6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -25737,23 +24306,18 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>New Journal is not in the menu; POST /api/v1/journals returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I7" s="27" t="inlineStr">
+          <t>New Journal is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="28" t="n"/>
-      <c r="M7" s="12" t="n"/>
+      <c r="K7" s="28" t="n"/>
+      <c r="L7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -25788,23 +24352,18 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>New Journal is not in the menu; POST /api/v1/journals returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I8" s="27" t="inlineStr">
+          <t>New Journal is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="28" t="n"/>
-      <c r="M8" s="12" t="n"/>
+      <c r="K8" s="28" t="n"/>
+      <c r="L8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -25839,23 +24398,18 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>New Journal is not in the menu; POST /api/v1/journals returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I9" s="27" t="inlineStr">
+          <t>New Journal is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="28" t="n"/>
-      <c r="M9" s="12" t="n"/>
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -25893,16 +24447,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="27" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="28" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="K10" s="28" t="n"/>
+      <c r="L10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -25940,16 +24493,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="28" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -25984,19 +24536,18 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Assign is not shown; POST /journals/assign returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="27" t="inlineStr">
+          <t>Assign is not shown; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="28" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -26034,16 +24585,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="27" t="inlineStr">
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="28" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="K13" s="28" t="n"/>
+      <c r="L13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -26081,16 +24631,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I14" s="12" t="n"/>
       <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="28" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -26125,19 +24674,18 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Post and Return to Maker are not shown; POST /journals/{id}/approve returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="27" t="inlineStr">
+          <t>Post and Return to Maker are not shown; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="28" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -26172,19 +24720,18 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Post and Return to Maker are not shown; POST /journals/{id}/approve returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="27" t="inlineStr">
+          <t>Post and Return to Maker are not shown; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="28" t="n"/>
-      <c r="M16" s="12" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -26222,16 +24769,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="27" t="inlineStr">
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="28" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -26266,19 +24812,18 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Reverse is not shown; POST /journals/{id}/reverse returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr"/>
-      <c r="I18" s="27" t="inlineStr">
+          <t>Reverse is not shown; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I18" s="12" t="n"/>
       <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="28" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -26313,19 +24858,18 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Reverse is not shown; POST /journals/{id}/reverse returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="27" t="inlineStr">
+          <t>Reverse is not shown; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
-      <c r="K19" s="12" t="n"/>
-      <c r="L19" s="28" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -26363,20 +24907,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="28" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="K20" s="28" t="n"/>
+      <c r="L20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -26411,23 +24950,18 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>The revaluation card has no entry; POST /currencies/revaluation-rates returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I21" s="27" t="inlineStr">
+          <t>The revaluation card has no entry; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I21" s="12" t="n"/>
       <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="28" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="K21" s="28" t="n"/>
+      <c r="L21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -26462,23 +24996,18 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>The revaluation card has no entry; POST /currencies/revaluation-rates returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I22" s="27" t="inlineStr">
+          <t>The revaluation card has no entry; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I22" s="12" t="n"/>
       <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="28" t="n"/>
-      <c r="M22" s="12" t="n"/>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -26516,20 +25045,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I23" s="27" t="inlineStr">
+      <c r="H23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I23" s="12" t="n"/>
       <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="28" t="n"/>
-      <c r="M23" s="12" t="n"/>
+      <c r="K23" s="28" t="n"/>
+      <c r="L23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -26564,23 +25088,18 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Chart Upload is not in the menu; POST /coa/uploads returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I24" s="27" t="inlineStr">
+          <t>Chart Upload is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I24" s="12" t="n"/>
       <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="28" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -26615,23 +25134,18 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Chart Upload is not in the menu; POST /coa/uploads returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I25" s="27" t="inlineStr">
+          <t>Chart Upload is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I25" s="12" t="n"/>
       <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="28" t="n"/>
-      <c r="M25" s="12" t="n"/>
+      <c r="K25" s="28" t="n"/>
+      <c r="L25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -26669,16 +25183,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr"/>
-      <c r="I26" s="27" t="inlineStr">
+      <c r="H26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="28" t="n"/>
-      <c r="M26" s="12" t="n"/>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -26716,16 +25229,15 @@
           <t>The pending accounts are not offered in My Approvals.</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr"/>
-      <c r="I27" s="27" t="inlineStr">
+      <c r="H27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I27" s="12" t="n"/>
       <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="28" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="K27" s="28" t="n"/>
+      <c r="L27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -26763,16 +25275,15 @@
           <t>The pending accounts are not offered in My Approvals.</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr"/>
-      <c r="I28" s="27" t="inlineStr">
+      <c r="H28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I28" s="12" t="n"/>
       <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="28" t="n"/>
-      <c r="M28" s="12" t="n"/>
+      <c r="K28" s="28" t="n"/>
+      <c r="L28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -26810,20 +25321,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I29" s="27" t="inlineStr">
+      <c r="H29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I29" s="12" t="n"/>
       <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="28" t="n"/>
-      <c r="M29" s="12" t="n"/>
+      <c r="K29" s="28" t="n"/>
+      <c r="L29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -26861,20 +25367,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I30" s="27" t="inlineStr">
+      <c r="H30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I30" s="12" t="n"/>
       <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="28" t="n"/>
-      <c r="M30" s="12" t="n"/>
+      <c r="K30" s="28" t="n"/>
+      <c r="L30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -26909,23 +25410,18 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>GL Close &amp; Cut-Off is not in the menu; POST /closing/close-schedules returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I31" s="27" t="inlineStr">
+          <t>GL Close &amp; Cut-Off is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I31" s="12" t="n"/>
       <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="28" t="n"/>
-      <c r="M31" s="12" t="n"/>
+      <c r="K31" s="28" t="n"/>
+      <c r="L31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -26960,23 +25456,18 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>GL Close &amp; Cut-Off is not in the menu; POST /closing/close-schedules returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>GlPlatformApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I32" s="27" t="inlineStr">
+          <t>GL Close &amp; Cut-Off is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I32" s="12" t="n"/>
       <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="28" t="n"/>
-      <c r="M32" s="12" t="n"/>
+      <c r="K32" s="28" t="n"/>
+      <c r="L32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -27014,16 +25505,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr"/>
-      <c r="I33" s="27" t="inlineStr">
+      <c r="H33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I33" s="12" t="n"/>
       <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="28" t="n"/>
-      <c r="M33" s="12" t="n"/>
+      <c r="K33" s="28" t="n"/>
+      <c r="L33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -27061,16 +25551,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr"/>
-      <c r="I34" s="27" t="inlineStr">
+      <c r="H34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I34" s="12" t="n"/>
       <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="12" t="n"/>
+      <c r="K34" s="28" t="n"/>
+      <c r="L34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -27108,16 +25597,15 @@
           <t>FX Revaluation and Period-End &amp; Year-End are not in the menu.</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr"/>
-      <c r="I35" s="27" t="inlineStr">
+      <c r="H35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I35" s="12" t="n"/>
       <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
-      <c r="L35" s="28" t="n"/>
-      <c r="M35" s="12" t="n"/>
+      <c r="K35" s="28" t="n"/>
+      <c r="L35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -27155,20 +25643,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I36" s="27" t="inlineStr">
+      <c r="H36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="28" t="n"/>
-      <c r="M36" s="12" t="n"/>
+      <c r="K36" s="28" t="n"/>
+      <c r="L36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -27206,20 +25689,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I37" s="27" t="inlineStr">
+      <c r="H37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I37" s="12" t="n"/>
       <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="28" t="n"/>
-      <c r="M37" s="12" t="n"/>
+      <c r="K37" s="28" t="n"/>
+      <c r="L37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -27257,20 +25735,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I38" s="27" t="inlineStr">
+      <c r="H38" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I38" s="12" t="n"/>
       <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="28" t="n"/>
-      <c r="M38" s="12" t="n"/>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -27308,20 +25781,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I39" s="27" t="inlineStr">
+      <c r="H39" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I39" s="12" t="n"/>
       <c r="J39" s="12" t="n"/>
-      <c r="K39" s="12" t="n"/>
-      <c r="L39" s="28" t="n"/>
-      <c r="M39" s="12" t="n"/>
+      <c r="K39" s="28" t="n"/>
+      <c r="L39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -27359,20 +25827,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I40" s="27" t="inlineStr">
+      <c r="H40" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I40" s="12" t="n"/>
       <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="28" t="n"/>
-      <c r="M40" s="12" t="n"/>
+      <c r="K40" s="28" t="n"/>
+      <c r="L40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -27407,23 +25870,18 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>Report Pack is not in the menu; GET /frbs/report-pack returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I41" s="27" t="inlineStr">
+          <t>Report Pack is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I41" s="12" t="n"/>
       <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
-      <c r="L41" s="28" t="n"/>
-      <c r="M41" s="12" t="n"/>
+      <c r="K41" s="28" t="n"/>
+      <c r="L41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -27458,23 +25916,18 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>Report Pack is not in the menu; GET /frbs/report-pack returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I42" s="27" t="inlineStr">
+          <t>Report Pack is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H42" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I42" s="12" t="n"/>
       <c r="J42" s="12" t="n"/>
-      <c r="K42" s="12" t="n"/>
-      <c r="L42" s="28" t="n"/>
-      <c r="M42" s="12" t="n"/>
+      <c r="K42" s="28" t="n"/>
+      <c r="L42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -27512,20 +25965,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I43" s="27" t="inlineStr">
+      <c r="H43" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I43" s="12" t="n"/>
       <c r="J43" s="12" t="n"/>
-      <c r="K43" s="12" t="n"/>
-      <c r="L43" s="28" t="n"/>
-      <c r="M43" s="12" t="n"/>
+      <c r="K43" s="28" t="n"/>
+      <c r="L43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -27563,20 +26011,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I44" s="27" t="inlineStr">
+      <c r="H44" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I44" s="12" t="n"/>
       <c r="J44" s="12" t="n"/>
-      <c r="K44" s="12" t="n"/>
-      <c r="L44" s="28" t="n"/>
-      <c r="M44" s="12" t="n"/>
+      <c r="K44" s="28" t="n"/>
+      <c r="L44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -27611,23 +26054,18 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>Service Fee Runs is not in the menu; POST /frbs/service-fee/runs returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I45" s="27" t="inlineStr">
+          <t>Service Fee Runs is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H45" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I45" s="12" t="n"/>
       <c r="J45" s="12" t="n"/>
-      <c r="K45" s="12" t="n"/>
-      <c r="L45" s="28" t="n"/>
-      <c r="M45" s="12" t="n"/>
+      <c r="K45" s="28" t="n"/>
+      <c r="L45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -27662,23 +26100,18 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>Service Fee Runs is not in the menu; POST /frbs/service-fee/runs returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I46" s="27" t="inlineStr">
+          <t>Service Fee Runs is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H46" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I46" s="12" t="n"/>
       <c r="J46" s="12" t="n"/>
-      <c r="K46" s="12" t="n"/>
-      <c r="L46" s="28" t="n"/>
-      <c r="M46" s="12" t="n"/>
+      <c r="K46" s="28" t="n"/>
+      <c r="L46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -27716,20 +26149,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I47" s="27" t="inlineStr">
+      <c r="H47" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I47" s="12" t="n"/>
       <c r="J47" s="12" t="n"/>
-      <c r="K47" s="12" t="n"/>
-      <c r="L47" s="28" t="n"/>
-      <c r="M47" s="12" t="n"/>
+      <c r="K47" s="28" t="n"/>
+      <c r="L47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -27767,20 +26195,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I48" s="27" t="inlineStr">
+      <c r="H48" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I48" s="12" t="n"/>
       <c r="J48" s="12" t="n"/>
-      <c r="K48" s="12" t="n"/>
-      <c r="L48" s="28" t="n"/>
-      <c r="M48" s="12" t="n"/>
+      <c r="K48" s="28" t="n"/>
+      <c r="L48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -27815,23 +26238,18 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>Approve and Service Fee Rates are not shown; the calls return HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>FrbsApiIT#permissionsAreEnforced</t>
-        </is>
-      </c>
-      <c r="I49" s="27" t="inlineStr">
+          <t>Approve and Service Fee Rates are not shown; direct requests are refused.</t>
+        </is>
+      </c>
+      <c r="H49" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I49" s="12" t="n"/>
       <c r="J49" s="12" t="n"/>
-      <c r="K49" s="12" t="n"/>
-      <c r="L49" s="28" t="n"/>
-      <c r="M49" s="12" t="n"/>
+      <c r="K49" s="28" t="n"/>
+      <c r="L49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -27869,16 +26287,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr"/>
-      <c r="I50" s="27" t="inlineStr">
+      <c r="H50" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I50" s="12" t="n"/>
       <c r="J50" s="12" t="n"/>
-      <c r="K50" s="12" t="n"/>
-      <c r="L50" s="28" t="n"/>
-      <c r="M50" s="12" t="n"/>
+      <c r="K50" s="28" t="n"/>
+      <c r="L50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -27916,16 +26333,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr"/>
-      <c r="I51" s="27" t="inlineStr">
+      <c r="H51" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I51" s="12" t="n"/>
       <c r="J51" s="12" t="n"/>
-      <c r="K51" s="12" t="n"/>
-      <c r="L51" s="28" t="n"/>
-      <c r="M51" s="12" t="n"/>
+      <c r="K51" s="28" t="n"/>
+      <c r="L51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -27963,16 +26379,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr"/>
-      <c r="I52" s="27" t="inlineStr">
+      <c r="H52" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I52" s="12" t="n"/>
       <c r="J52" s="12" t="n"/>
-      <c r="K52" s="12" t="n"/>
-      <c r="L52" s="28" t="n"/>
-      <c r="M52" s="12" t="n"/>
+      <c r="K52" s="28" t="n"/>
+      <c r="L52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -28010,16 +26425,15 @@
           <t>BIR Forms &amp; Books is not in the menu.</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr"/>
-      <c r="I53" s="27" t="inlineStr">
+      <c r="H53" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I53" s="12" t="n"/>
       <c r="J53" s="12" t="n"/>
-      <c r="K53" s="12" t="n"/>
-      <c r="L53" s="28" t="n"/>
-      <c r="M53" s="12" t="n"/>
+      <c r="K53" s="28" t="n"/>
+      <c r="L53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -28057,16 +26471,15 @@
           <t>BIR Forms &amp; Books is not in the menu.</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr"/>
-      <c r="I54" s="27" t="inlineStr">
+      <c r="H54" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I54" s="12" t="n"/>
       <c r="J54" s="12" t="n"/>
-      <c r="K54" s="12" t="n"/>
-      <c r="L54" s="28" t="n"/>
-      <c r="M54" s="12" t="n"/>
+      <c r="K54" s="28" t="n"/>
+      <c r="L54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -28104,16 +26517,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H55" s="12" t="inlineStr"/>
-      <c r="I55" s="27" t="inlineStr">
+      <c r="H55" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I55" s="12" t="n"/>
       <c r="J55" s="12" t="n"/>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="28" t="n"/>
-      <c r="M55" s="12" t="n"/>
+      <c r="K55" s="28" t="n"/>
+      <c r="L55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -28148,19 +26560,18 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>Add and Edit are not shown on Lists of Values; POST /lov/{type}/values returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H56" s="12" t="inlineStr"/>
-      <c r="I56" s="27" t="inlineStr">
+          <t>Add and Edit are not shown on Lists of Values; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H56" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I56" s="12" t="n"/>
       <c r="J56" s="12" t="n"/>
-      <c r="K56" s="12" t="n"/>
-      <c r="L56" s="28" t="n"/>
-      <c r="M56" s="12" t="n"/>
+      <c r="K56" s="28" t="n"/>
+      <c r="L56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -28195,19 +26606,18 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>Add and Edit are not shown on Lists of Values; POST /lov/{type}/values returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H57" s="12" t="inlineStr"/>
-      <c r="I57" s="27" t="inlineStr">
+          <t>Add and Edit are not shown on Lists of Values; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H57" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I57" s="12" t="n"/>
       <c r="J57" s="12" t="n"/>
-      <c r="K57" s="12" t="n"/>
-      <c r="L57" s="28" t="n"/>
-      <c r="M57" s="12" t="n"/>
+      <c r="K57" s="28" t="n"/>
+      <c r="L57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -28242,19 +26652,18 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>Add and Edit are not shown on Lists of Values; POST /lov/{type}/values returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H58" s="12" t="inlineStr"/>
-      <c r="I58" s="27" t="inlineStr">
+          <t>Add and Edit are not shown on Lists of Values; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H58" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I58" s="12" t="n"/>
       <c r="J58" s="12" t="n"/>
-      <c r="K58" s="12" t="n"/>
-      <c r="L58" s="28" t="n"/>
-      <c r="M58" s="12" t="n"/>
+      <c r="K58" s="28" t="n"/>
+      <c r="L58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -28292,20 +26701,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H59" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestIT#requestsAreValidatedAndDecidedUnderFourEyes</t>
-        </is>
-      </c>
-      <c r="I59" s="27" t="inlineStr">
+      <c r="H59" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I59" s="12" t="n"/>
       <c r="J59" s="12" t="n"/>
-      <c r="K59" s="12" t="n"/>
-      <c r="L59" s="28" t="n"/>
-      <c r="M59" s="12" t="n"/>
+      <c r="K59" s="28" t="n"/>
+      <c r="L59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -28343,20 +26747,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestIT#requestsAreValidatedAndDecidedUnderFourEyes</t>
-        </is>
-      </c>
-      <c r="I60" s="27" t="inlineStr">
+      <c r="H60" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I60" s="12" t="n"/>
       <c r="J60" s="12" t="n"/>
-      <c r="K60" s="12" t="n"/>
-      <c r="L60" s="28" t="n"/>
-      <c r="M60" s="12" t="n"/>
+      <c r="K60" s="28" t="n"/>
+      <c r="L60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -28391,23 +26790,18 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>New Request is not shown; POST /nbadmin/access-requests returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H61" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestIT#requestsAreValidatedAndDecidedUnderFourEyes</t>
-        </is>
-      </c>
-      <c r="I61" s="27" t="inlineStr">
+          <t>New Request is not shown; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H61" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I61" s="12" t="n"/>
       <c r="J61" s="12" t="n"/>
-      <c r="K61" s="12" t="n"/>
-      <c r="L61" s="28" t="n"/>
-      <c r="M61" s="12" t="n"/>
+      <c r="K61" s="28" t="n"/>
+      <c r="L61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -28442,23 +26836,18 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>New Request is not shown; POST /nbadmin/access-requests returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H62" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestIT#requestsAreValidatedAndDecidedUnderFourEyes</t>
-        </is>
-      </c>
-      <c r="I62" s="27" t="inlineStr">
+          <t>New Request is not shown; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H62" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I62" s="12" t="n"/>
       <c r="J62" s="12" t="n"/>
-      <c r="K62" s="12" t="n"/>
-      <c r="L62" s="28" t="n"/>
-      <c r="M62" s="12" t="n"/>
+      <c r="K62" s="28" t="n"/>
+      <c r="L62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -28496,20 +26885,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H63" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestIT#requestsAreValidatedAndDecidedUnderFourEyes</t>
-        </is>
-      </c>
-      <c r="I63" s="27" t="inlineStr">
+      <c r="H63" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I63" s="12" t="n"/>
       <c r="J63" s="12" t="n"/>
-      <c r="K63" s="12" t="n"/>
-      <c r="L63" s="28" t="n"/>
-      <c r="M63" s="12" t="n"/>
+      <c r="K63" s="28" t="n"/>
+      <c r="L63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -28544,23 +26928,18 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>The access requests are not offered in My Approvals; the approve call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H64" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestIT#requestsAreValidatedAndDecidedUnderFourEyes</t>
-        </is>
-      </c>
-      <c r="I64" s="27" t="inlineStr">
+          <t>The access requests are not offered in My Approvals; a direct approve request is refused.</t>
+        </is>
+      </c>
+      <c r="H64" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I64" s="12" t="n"/>
       <c r="J64" s="12" t="n"/>
-      <c r="K64" s="12" t="n"/>
-      <c r="L64" s="28" t="n"/>
-      <c r="M64" s="12" t="n"/>
+      <c r="K64" s="28" t="n"/>
+      <c r="L64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -28595,23 +26974,18 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>The access requests are not offered in My Approvals; the approve call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H65" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestIT#requestsAreValidatedAndDecidedUnderFourEyes</t>
-        </is>
-      </c>
-      <c r="I65" s="27" t="inlineStr">
+          <t>The access requests are not offered in My Approvals; a direct approve request is refused.</t>
+        </is>
+      </c>
+      <c r="H65" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I65" s="12" t="n"/>
       <c r="J65" s="12" t="n"/>
-      <c r="K65" s="12" t="n"/>
-      <c r="L65" s="28" t="n"/>
-      <c r="M65" s="12" t="n"/>
+      <c r="K65" s="28" t="n"/>
+      <c r="L65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -28646,30 +27020,25 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>The access requests are not offered in My Approvals; the approve call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H66" s="12" t="inlineStr">
-        <is>
-          <t>AccessRequestIT#requestsAreValidatedAndDecidedUnderFourEyes</t>
-        </is>
-      </c>
-      <c r="I66" s="27" t="inlineStr">
+          <t>The access requests are not offered in My Approvals; a direct approve request is refused.</t>
+        </is>
+      </c>
+      <c r="H66" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I66" s="12" t="n"/>
       <c r="J66" s="12" t="n"/>
-      <c r="K66" s="12" t="n"/>
-      <c r="L66" s="28" t="n"/>
-      <c r="M66" s="12" t="n"/>
+      <c r="K66" s="28" t="n"/>
+      <c r="L66" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M66"/>
+  <autoFilter ref="A4:L66"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I566">
+  <conditionalFormatting sqref="H5:H566">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -28683,7 +27052,7 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:M566">
+  <conditionalFormatting sqref="A5:L566">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -28692,7 +27061,7 @@
     <dataValidation sqref="F5:F566" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Access" error="Choose a value from the list (Access)." type="list">
       <formula1>'_lists'!$F$1:$F$2</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I566" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="H5:H566" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$G$1:$G$5</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Drop-1_Transactional/BRD-05_Accounting_Disbursement_ACSL/BIBS_TestPlan_BRD-05_Accounting_Disbursement_ACSL_Vol1_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-05_Accounting_Disbursement_ACSL/BIBS_TestPlan_BRD-05_Accounting_Disbursement_ACSL_Vol1_v1.0.xlsx
@@ -6813,8 +6813,8 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>The account is locked until the System Administrator unlocks it.
-Message "Account is locked. Contact your administrator." (AUTHENTICATION_FAILED).</t>
+          <t>The account locks at the third failure; the correct password is refused with the same message as a wrong password until the System Administrator unlocks it in Administration &gt; Users, where the lock shows.
+Message "Invalid user name or password" (AUTHENTICATION_FAILED).</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I51" s="12" t="inlineStr"/>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I54" s="12" t="inlineStr"/>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I66" s="12" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>Ten submitted journals, one made unbalanced by the test lead in the database.
+          <t>Ten submitted journals, one made unbalanced by the test lead in the test environment.
 Data: TD-AC-05 Journals keyed in the test</t>
         </is>
       </c>
@@ -12297,7 +12297,7 @@
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I86" s="12" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr"/>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="H165" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I165" s="12" t="inlineStr">
@@ -18225,7 +18225,7 @@
       </c>
       <c r="H171" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I171" s="12" t="inlineStr">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="H181" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I181" s="12" t="inlineStr">
